--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45798</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44896</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45723</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
         <v>17</v>
       </c>
       <c r="T4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45723</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45723</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45917</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>45579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>46120</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>45922</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45783</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>45411</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45086</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45922</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>46146</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>46120</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45817</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>45880</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>45441</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>46120</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>45679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>46195</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>45723</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>45742</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45441</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>45917</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45968</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>45917</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>44578</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>46048</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45964</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45048</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>45336</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45782</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>45789</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>45421</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45905</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45373</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>45042</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>45764</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>45884</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>46120</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>45954</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>45604</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>46218</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45833</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44622</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45579</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45733</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>46136</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>45917</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>44931</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44746</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>45702</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>45013</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>45133</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>46037</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44977</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>45258</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>46198</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>45727</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>46135</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44981</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>46213</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>46212</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45016</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>46268</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>45796</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>45860</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44524</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44557</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>45742</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>45583</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44993</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>44974</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44789</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45086</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45895</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>45334</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>45936</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>45905</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>45721</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>45769</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45716</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>44957</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>45394</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45978</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45985</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>45694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>44886</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>46043</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45056</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>46086</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>44742</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>45201</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>46198</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>46199</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>46199</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>45716</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45414</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>45758</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>45797</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>46218</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>46218</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>46219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45763</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45783</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>46282</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>45369</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44915</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>45791</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45918</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>44480</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>44524</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>44813</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>44490</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>44475</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>44777</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45362</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>45583</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>45702</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45174</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>45363</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>44935</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45096</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45744</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45744</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>44943</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45317</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>46139</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45894</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>45894</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45905</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>45904</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>45645</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45771</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>45924</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45090</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45250</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45733</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44974</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44897</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45580</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>45008</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45117</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>46163</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>44652</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>45201</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>46038</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>45096</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>46178</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>45117</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>46079</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>46084</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>46202</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45408</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45043</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45376</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45405</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>46217</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45251</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>46218</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>46219</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>46225</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45726</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>46231</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>46241</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45583</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>45833</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44504</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45845</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45798</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44596</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>44529</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>44530</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44582</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>44502</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>44537</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>44825</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>44739</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>44719</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>44503</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>44865</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>44524</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44696</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>44494</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>44671</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44713</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>44530</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>44515</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>44571</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>44475</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>44475</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>44630</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>44530</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>44503</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44459</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44879</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>44459</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44475</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>44574</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>44686</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>44602</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>44889</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>44825</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44582</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44825</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44741</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>44730</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44578</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>44886</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>44740</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>44874</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44726</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>44487</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>44596</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>44468</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>44630</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44869</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45678</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45401</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>44651</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44826</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45106</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45469</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>44900</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>45118</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>44783</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>45086</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45076</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>44512</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>45386</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45706</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44935</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45093</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45716</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45053</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44861</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>44998</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45110</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45266</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44957</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45356</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45092</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>44974</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>45636</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45313</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45238</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>45742</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>44741</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>45386</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>45043</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>45022</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>44970</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45254</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>44862</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>45583</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45535</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>45356</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>44980</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>44956</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45246</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>44966</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>44575</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45414</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44936</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45274</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45603</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>45400</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45174</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45174</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45628</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>44935</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>44950</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>44897</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>44644</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>44896</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44858</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45436</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>45758</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>45110</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45110</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>44754</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>45202</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>45532</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45597</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45121</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45678</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>45317</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>45071</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45678</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44889</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>45202</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>45043</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45478</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>45098</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>45414</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45764</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>45757</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>45183</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>45043</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45240</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45118</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45715</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45215</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>44536</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45153</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45049</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45330</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45468</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>44980</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45096</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45201</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45219</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45317</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45365</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>45405</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44599</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>45769</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>44923</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44999</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44930</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45886</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45966</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>45889</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45796</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>45043</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>45092</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>44970</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>44865</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>44943</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45211</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45211</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45520</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45888</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45888</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45215</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45891</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45436</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>45204</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45356</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45215</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>45895</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>45895</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>45894</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>45894</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>45141</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>45896</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>44945</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33581,7 +33581,7 @@
         <v>45896</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>46139</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>45887</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>45887</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>44936</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>45898</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>45817</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34097,7 +34097,7 @@
         <v>45903</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>45006</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45903</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>45867</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45582</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>45836</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>45178</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>46139</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45908</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>45908</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45386</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>44825</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>45917</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>45917</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>45030</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>44939</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>45922</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35373,7 +35373,7 @@
         <v>45093</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45012</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>45922</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45924</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>45153</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45924</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>45709</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35909,7 +35909,7 @@
         <v>45924</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45926</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>44867</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45373</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>44980</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>45016</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36367,7 +36367,7 @@
         <v>45930</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36440,7 +36440,7 @@
         <v>45254</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>45742</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45497</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44861</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>44607</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>45629</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>45936</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45716</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>45106</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37117,7 +37117,7 @@
         <v>45706</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37190,7 +37190,7 @@
         <v>46146</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37268,7 +37268,7 @@
         <v>45769</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>45266</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45873</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45435</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37560,7 +37560,7 @@
         <v>44977</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
         <v>45709</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37716,7 +37716,7 @@
         <v>45943</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>46146</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37867,7 +37867,7 @@
         <v>45114</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37940,7 +37940,7 @@
         <v>44630</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45008</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>44783</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>44977</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>44719</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>45012</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>45310</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>45706</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>45761</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>45153</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>45490</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38768,7 +38768,7 @@
         <v>45960</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>45370</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38924,7 +38924,7 @@
         <v>44805</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45960</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39080,7 +39080,7 @@
         <v>45961</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>44907</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>45117</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>45121</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>45733</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>44767</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45769</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>45072</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>45106</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44853</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         <v>45975</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39908,7 +39908,7 @@
         <v>45629</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45478</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45727</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45976</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45090</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40288,7 +40288,7 @@
         <v>45758</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44936</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>44462</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45205</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>45985</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>45446</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>45446</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45985</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45077</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>45092</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45278</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45986</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>45030</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>45399</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>45986</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45547</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45159</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>45121</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41642,7 +41642,7 @@
         <v>45699</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45699</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41788,7 +41788,7 @@
         <v>44910</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>44928</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45637</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>45117</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45369</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>45678</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>45014</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>45266</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>45049</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45049</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>45266</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>45237</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>46163</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>44974</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         <v>44965</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>44834</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>45432</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>44596</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>46007</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>46006</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>46006</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>46007</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>46006</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>46006</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43605,7 +43605,7 @@
         <v>45771</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>45546</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>45889</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
         <v>45229</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45030</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>45030</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44048,7 +44048,7 @@
         <v>45188</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44121,7 +44121,7 @@
         <v>46010</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44194,7 +44194,7 @@
         <v>46010</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44267,7 +44267,7 @@
         <v>46010</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44340,7 +44340,7 @@
         <v>46010</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45629</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44486,7 +44486,7 @@
         <v>45268</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45550</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>46061</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45053</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44778,7 +44778,7 @@
         <v>44860</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>44597</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45014</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44997,7 +44997,7 @@
         <v>44936</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45723</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>44588</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>46030</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>46010</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45367,7 +45367,7 @@
         <v>46030</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>46035</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>44494</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>46037</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45669,7 +45669,7 @@
         <v>46041</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45747,7 +45747,7 @@
         <v>46038</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45820,7 +45820,7 @@
         <v>46042</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>46042</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45274</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46039,7 +46039,7 @@
         <v>46043</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>46042</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46185,7 +46185,7 @@
         <v>45558</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>44859</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45336</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>44582</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45442</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45183</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>45183</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>46045</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>46048</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>45043</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>46046</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>46046</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47071,7 +47071,7 @@
         <v>46048</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45509</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>46055</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47300,7 +47300,7 @@
         <v>45145</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>46175</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>46052</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>46178</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>46052</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>46052</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>46052</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45215</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>46178</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>46178</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>44936</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>44890</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48181,7 +48181,7 @@
         <v>45769</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48254,7 +48254,7 @@
         <v>45013</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>44956</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48405,7 +48405,7 @@
         <v>46178</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>46178</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48551,7 +48551,7 @@
         <v>44721</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>46178</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>46178</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>46182</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48843,7 +48843,7 @@
         <v>45763</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45217</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48994,7 +48994,7 @@
         <v>45191</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>46181</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49140,7 +49140,7 @@
         <v>46072</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>46182</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49291,7 +49291,7 @@
         <v>46072</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>45733</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>46182</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>46076</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49593,7 +49593,7 @@
         <v>46076</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>46076</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>44803</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>44860</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49885,7 +49885,7 @@
         <v>46079</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>46155</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>46079</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>44939</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
         <v>44956</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45379</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>46188</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>44677</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>46090</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>46185</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50640,7 +50640,7 @@
         <v>45126</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45126</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>46188</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>46185</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45268</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>44907</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>45114</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51166,7 +51166,7 @@
         <v>45114</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>46092</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51312,7 +51312,7 @@
         <v>46072</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51385,7 +51385,7 @@
         <v>46092</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>44469</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51531,7 +51531,7 @@
         <v>46072</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>46093</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>46093</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45723</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>46094</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>46094</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51979,7 +51979,7 @@
         <v>46093</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>46094</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52130,7 +52130,7 @@
         <v>46093</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>46181</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52276,7 +52276,7 @@
         <v>44679</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45359</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52427,7 +52427,7 @@
         <v>46196</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52500,7 +52500,7 @@
         <v>45796</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>46101</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52656,7 +52656,7 @@
         <v>46196</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         <v>46196</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52807,7 +52807,7 @@
         <v>46196</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>46196</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>46197</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53031,7 +53031,7 @@
         <v>46101</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>46106</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>44880</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53265,7 +53265,7 @@
         <v>46198</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>46108</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>46107</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53494,7 +53494,7 @@
         <v>46198</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53567,7 +53567,7 @@
         <v>46198</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53645,7 +53645,7 @@
         <v>44936</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>44936</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53801,7 +53801,7 @@
         <v>45747</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53874,7 +53874,7 @@
         <v>45769</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53947,7 +53947,7 @@
         <v>46112</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54020,7 +54020,7 @@
         <v>44488</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54093,7 +54093,7 @@
         <v>44994</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45028</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45442</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>46244</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54385,7 +54385,7 @@
         <v>46244</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
         <v>45408</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>46120</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54604,7 +54604,7 @@
         <v>46120</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>45106</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54755,7 +54755,7 @@
         <v>46120</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54828,7 +54828,7 @@
         <v>44862</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54906,7 +54906,7 @@
         <v>46202</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54979,7 +54979,7 @@
         <v>46245</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55057,7 +55057,7 @@
         <v>46199</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55130,7 +55130,7 @@
         <v>46199</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55203,7 +55203,7 @@
         <v>46244</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>46244</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55354,7 +55354,7 @@
         <v>46244</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>46199</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>46245</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>46128</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55656,7 +55656,7 @@
         <v>46245</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>46128</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55807,7 +55807,7 @@
         <v>44805</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55885,7 +55885,7 @@
         <v>45201</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55958,7 +55958,7 @@
         <v>45132</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56036,7 +56036,7 @@
         <v>45373</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56109,7 +56109,7 @@
         <v>46199</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56187,7 +56187,7 @@
         <v>44992</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>45252</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>45369</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>45673</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56479,7 +56479,7 @@
         <v>45128</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>45741</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>46135</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>46135</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56781,7 +56781,7 @@
         <v>45891</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56854,7 +56854,7 @@
         <v>45657</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45096</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57010,7 +57010,7 @@
         <v>46204</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57088,7 +57088,7 @@
         <v>45246</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57161,7 +57161,7 @@
         <v>45246</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>46139</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45174</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>45174</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57453,7 +57453,7 @@
         <v>44641</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57526,7 +57526,7 @@
         <v>45457</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57599,7 +57599,7 @@
         <v>45884</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57677,7 +57677,7 @@
         <v>45924</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57750,7 +57750,7 @@
         <v>45092</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57823,7 +57823,7 @@
         <v>45254</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57901,7 +57901,7 @@
         <v>45027</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57974,7 +57974,7 @@
         <v>45425</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45833</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58120,7 +58120,7 @@
         <v>45581</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58193,7 +58193,7 @@
         <v>45091</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58271,7 +58271,7 @@
         <v>45369</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58344,7 +58344,7 @@
         <v>46203</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>45043</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58490,7 +58490,7 @@
         <v>45442</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58568,7 +58568,7 @@
         <v>45008</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58641,7 +58641,7 @@
         <v>45339</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58714,7 +58714,7 @@
         <v>45758</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58787,7 +58787,7 @@
         <v>46206</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58860,7 +58860,7 @@
         <v>45093</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58933,7 +58933,7 @@
         <v>44992</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59006,7 +59006,7 @@
         <v>44980</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59084,7 +59084,7 @@
         <v>46206</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59157,7 +59157,7 @@
         <v>45453</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45252</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59303,7 +59303,7 @@
         <v>45636</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59376,7 +59376,7 @@
         <v>45636</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59449,7 +59449,7 @@
         <v>44573</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59522,7 +59522,7 @@
         <v>45330</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59595,7 +59595,7 @@
         <v>44862</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>44573</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59746,7 +59746,7 @@
         <v>45110</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59824,7 +59824,7 @@
         <v>44713</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59897,7 +59897,7 @@
         <v>46043</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59970,7 +59970,7 @@
         <v>46213</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60048,7 +60048,7 @@
         <v>46216</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60126,7 +60126,7 @@
         <v>46258</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60204,7 +60204,7 @@
         <v>46258</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60282,7 +60282,7 @@
         <v>46258</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60360,7 +60360,7 @@
         <v>45798</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60438,7 +60438,7 @@
         <v>45112</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60511,7 +60511,7 @@
         <v>45043</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60589,7 +60589,7 @@
         <v>46213</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>46258</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60745,7 +60745,7 @@
         <v>46258</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60823,7 +60823,7 @@
         <v>46213</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>46043</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60974,7 +60974,7 @@
         <v>46260</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61052,7 +61052,7 @@
         <v>44739</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61125,7 +61125,7 @@
         <v>46218</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61203,7 +61203,7 @@
         <v>45317</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61281,7 +61281,7 @@
         <v>46217</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61359,7 +61359,7 @@
         <v>46218</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45432</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61510,7 +61510,7 @@
         <v>46217</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>46260</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61666,7 +61666,7 @@
         <v>45715</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61744,7 +61744,7 @@
         <v>46265</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61822,7 +61822,7 @@
         <v>45726</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61895,7 +61895,7 @@
         <v>45723</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61968,7 +61968,7 @@
         <v>46265</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62046,7 +62046,7 @@
         <v>45030</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62119,7 +62119,7 @@
         <v>45030</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62192,7 +62192,7 @@
         <v>45254</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62270,7 +62270,7 @@
         <v>45205</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>44851</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45129</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62489,7 +62489,7 @@
         <v>45478</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62567,7 +62567,7 @@
         <v>46178</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62640,7 +62640,7 @@
         <v>44957</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62718,7 +62718,7 @@
         <v>45403</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>46269</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62869,7 +62869,7 @@
         <v>45033</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45593</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63020,7 +63020,7 @@
         <v>45037</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63093,7 +63093,7 @@
         <v>46268</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63171,7 +63171,7 @@
         <v>45030</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63244,7 +63244,7 @@
         <v>45048</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63317,7 +63317,7 @@
         <v>46269</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63395,7 +63395,7 @@
         <v>46225</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63473,7 +63473,7 @@
         <v>45777</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63551,7 +63551,7 @@
         <v>45783</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63624,7 +63624,7 @@
         <v>45782</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63697,7 +63697,7 @@
         <v>46240</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63770,7 +63770,7 @@
         <v>45671</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63843,7 +63843,7 @@
         <v>45784</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63916,7 +63916,7 @@
         <v>46231</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63994,7 +63994,7 @@
         <v>46233</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64072,7 +64072,7 @@
         <v>46233</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64150,7 +64150,7 @@
         <v>46233</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64228,7 +64228,7 @@
         <v>46233</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64306,7 +64306,7 @@
         <v>45784</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         <v>46279</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64462,7 +64462,7 @@
         <v>45786</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64540,7 +64540,7 @@
         <v>45786</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64618,7 +64618,7 @@
         <v>46233</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64696,7 +64696,7 @@
         <v>46233</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64774,7 +64774,7 @@
         <v>46233</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64852,7 +64852,7 @@
         <v>46233</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64930,7 +64930,7 @@
         <v>46233</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65008,7 +65008,7 @@
         <v>44565</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65086,7 +65086,7 @@
         <v>45092</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>46233</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>46280</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65315,7 +65315,7 @@
         <v>45453</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65388,7 +65388,7 @@
         <v>45453</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65461,7 +65461,7 @@
         <v>46280</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65539,7 +65539,7 @@
         <v>45310</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65612,7 +65612,7 @@
         <v>46280</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65685,7 +65685,7 @@
         <v>45790</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65758,7 +65758,7 @@
         <v>46280</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65836,7 +65836,7 @@
         <v>45259</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65909,7 +65909,7 @@
         <v>45796</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65987,7 +65987,7 @@
         <v>45678</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66060,7 +66060,7 @@
         <v>46050</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66138,7 +66138,7 @@
         <v>45796</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66211,7 +66211,7 @@
         <v>46283</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66289,7 +66289,7 @@
         <v>45798</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66362,7 +66362,7 @@
         <v>45408</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66440,7 +66440,7 @@
         <v>45565</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66513,7 +66513,7 @@
         <v>45798</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66591,7 +66591,7 @@
         <v>46241</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66664,7 +66664,7 @@
         <v>46282</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66742,7 +66742,7 @@
         <v>45554</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66815,7 +66815,7 @@
         <v>45722</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66888,7 +66888,7 @@
         <v>46241</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66961,7 +66961,7 @@
         <v>45803</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67034,7 +67034,7 @@
         <v>45762</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67107,7 +67107,7 @@
         <v>45804</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67185,7 +67185,7 @@
         <v>45369</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67263,7 +67263,7 @@
         <v>45817</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67341,7 +67341,7 @@
         <v>45820</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67414,7 +67414,7 @@
         <v>45820</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67487,7 +67487,7 @@
         <v>45824</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67565,7 +67565,7 @@
         <v>45833</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67638,7 +67638,7 @@
         <v>45832</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67711,7 +67711,7 @@
         <v>45840</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67784,7 +67784,7 @@
         <v>45845</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67862,7 +67862,7 @@
         <v>45678</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67935,7 +67935,7 @@
         <v>45736</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -68008,7 +68008,7 @@
         <v>45706</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68081,7 +68081,7 @@
         <v>45796</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -68154,7 +68154,7 @@
         <v>45881</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -68232,7 +68232,7 @@
         <v>45883</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -68305,7 +68305,7 @@
         <v>45883</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -68378,7 +68378,7 @@
         <v>45883</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -68456,7 +68456,7 @@
         <v>45883</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -68529,7 +68529,7 @@
         <v>44130</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68602,7 +68602,7 @@
         <v>44313</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -68675,7 +68675,7 @@
         <v>44230</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -68748,7 +68748,7 @@
         <v>45316</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68821,7 +68821,7 @@
         <v>44638</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68899,7 +68899,7 @@
         <v>44649</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -68977,7 +68977,7 @@
         <v>44551</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -69050,7 +69050,7 @@
         <v>45629</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -69123,7 +69123,7 @@
         <v>45571</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -69196,7 +69196,7 @@
         <v>45432</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -69269,7 +69269,7 @@
         <v>44692</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -69342,7 +69342,7 @@
         <v>45571</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -69415,7 +69415,7 @@
         <v>45789</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -69488,7 +69488,7 @@
         <v>45784</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45798</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44896</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45723</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45723</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45723</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45917</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>46120</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45579</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>45783</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45922</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>45411</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45922</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>46120</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
         <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>45817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>46146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>45086</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>45880</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>45441</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>46120</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>45679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>45742</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>46195</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45723</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45917</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>45968</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>45441</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>46048</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45917</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44578</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45964</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45336</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>45048</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45782</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>45789</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>45373</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45905</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>45884</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>46120</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>45042</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45833</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>45764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>45604</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>45954</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>46218</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>45421</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44622</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45258</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45796</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>45133</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>46037</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>45917</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>45579</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>44931</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>46136</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>46135</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>45727</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45733</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>45702</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>45013</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45860</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>44977</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>46198</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>46213</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>46212</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>46268</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>45016</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>44981</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44524</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44557</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>44789</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>45414</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>45334</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>44886</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45895</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>46043</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>45201</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>46086</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>45936</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>45394</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45905</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>45978</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>44993</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>45985</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>44742</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>45694</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>44880</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45742</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>45758</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>45583</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>45369</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>46198</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>46199</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>46199</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>45716</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45797</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>46218</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>46218</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>46219</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>45716</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>45769</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>46282</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>44957</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45056</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>45086</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>44974</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45721</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>45763</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>45783</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44915</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>45791</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45918</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>44480</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>44524</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>44813</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>44475</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>44490</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45363</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>45117</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>46038</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>45894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45894</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>45904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>45905</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>45771</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>46079</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>46084</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>44943</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45251</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45317</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>45008</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45583</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>45580</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45645</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45583</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45096</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>45117</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45702</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45733</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>46139</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45090</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45833</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44504</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>46163</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45845</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45408</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45798</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>46178</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45376</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45362</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>46202</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>45201</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45096</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>46217</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>46218</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>46219</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>46225</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>44974</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>44777</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>46231</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45043</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44897</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>46241</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>46288</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>45174</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45924</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>44652</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45744</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45744</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>44935</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45250</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45405</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45726</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44596</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44529</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>44530</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44582</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44502</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>44537</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>44825</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>44739</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20940,7 +20940,7 @@
         <v>44719</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>44503</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>44865</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21164,7 +21164,7 @@
         <v>44524</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44696</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>44494</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>44671</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>44713</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44530</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>44515</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>44571</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>44475</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>44475</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44630</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>44530</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>44503</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44879</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44475</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>44574</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>44686</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44602</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>44889</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>44825</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>44582</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>44825</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44741</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>44730</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>44578</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>44886</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44740</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>44874</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>44726</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44487</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44596</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>44468</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>44630</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44869</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>45405</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>45709</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45043</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45215</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45268</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>44865</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44825</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>45072</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>44862</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45202</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45532</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45043</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>44805</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>45118</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>45369</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>45336</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45092</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>45037</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>44860</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>44862</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45386</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>45317</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>45425</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>45359</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>44880</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45128</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>45317</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>44861</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>44939</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45278</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>44858</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>45678</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45883</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>45093</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>45796</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45883</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44488</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>45096</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45796</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>46010</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45259</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>46030</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45266</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45490</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>44930</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>45798</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>44936</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>46030</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45798</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45888</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>45887</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>46035</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45888</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45887</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44890</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45565</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>46038</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45408</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45414</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28138,7 +28138,7 @@
         <v>46037</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45894</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>46042</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>46042</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45894</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>46042</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28591,7 +28591,7 @@
         <v>45896</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         <v>45896</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45895</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45895</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45554</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>46041</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>46043</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>45898</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44582</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>46046</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>46048</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>46048</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>46046</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45817</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45722</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>46045</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45903</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45903</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>46052</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>46052</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45908</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45908</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>45202</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>46052</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>46052</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>46055</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45365</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>45442</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>45803</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>44936</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45804</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45030</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45917</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>44889</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45917</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45028</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45922</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45922</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>44910</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>45762</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45924</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>45924</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45924</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>46072</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>46072</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>45106</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>46076</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>46076</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>45926</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45201</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>45930</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>46079</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>46079</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>45369</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45215</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45678</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>44936</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>44974</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>45369</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>44943</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>45936</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>46072</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>46072</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>45873</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>46090</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45174</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>45174</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>46092</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>46092</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>46093</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>46093</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>46093</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>46093</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>46094</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>45453</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>46094</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>46094</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45943</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45238</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>46101</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>46101</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45049</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45091</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45112</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>46107</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>44677</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>46106</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>46108</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>44834</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>46112</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>44741</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>45960</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>45960</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44965</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45014</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45961</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>46120</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>44956</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>46120</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>46120</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45356</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45636</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>44719</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45581</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>44573</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45414</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>44998</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44512</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>44970</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>46128</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>44980</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45975</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45976</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>46128</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45386</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>44721</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37254,7 +37254,7 @@
         <v>45114</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>45986</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45836</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45985</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>45986</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45884</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45889</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45985</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45924</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>46135</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>46135</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38087,7 +38087,7 @@
         <v>45657</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>45629</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>45098</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>44805</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45833</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>45117</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>45582</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45597</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45966</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45469</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45726</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38910,7 +38910,7 @@
         <v>44713</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>45121</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45891</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39134,7 +39134,7 @@
         <v>45891</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>45520</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>45747</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>45201</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>45030</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>45030</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>44853</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39645,7 +39645,7 @@
         <v>44999</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39723,7 +39723,7 @@
         <v>46139</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>45886</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45110</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39947,7 +39947,7 @@
         <v>44826</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40020,7 +40020,7 @@
         <v>45442</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>45817</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45178</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>45442</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>45820</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>46006</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>46006</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>46006</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>45008</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>44980</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40790,7 +40790,7 @@
         <v>46006</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>45013</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>46007</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45820</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>45229</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>46007</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>45796</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>46010</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45764</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>46010</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>46010</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>46010</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>45715</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>44992</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>45824</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41910,7 +41910,7 @@
         <v>44575</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>44957</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>44945</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>45093</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45110</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>46139</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>45274</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>46139</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45867</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>45254</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45077</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45509</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45043</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45183</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>45049</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45049</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44939</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
         <v>45012</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>45237</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>45769</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>45769</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43473,7 +43473,7 @@
         <v>45769</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>45733</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43624,7 +43624,7 @@
         <v>46146</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>44860</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>46146</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>45741</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>44896</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>44900</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>45832</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>45769</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>44897</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44311,7 +44311,7 @@
         <v>44928</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>44923</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45833</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44540,7 +44540,7 @@
         <v>44907</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44613,7 +44613,7 @@
         <v>44588</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44686,7 +44686,7 @@
         <v>45436</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>44783</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>45840</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>45716</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45369</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45678</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>45106</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>45379</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45845</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>46163</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45426,7 +45426,7 @@
         <v>45240</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45629</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45736</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>46061</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45432</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>45339</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>45408</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45254</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>45889</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>44607</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>44950</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>45092</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45006</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45706</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>45030</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45030</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>44994</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45110</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45110</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>46175</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46896,7 +46896,7 @@
         <v>45132</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46974,7 +46974,7 @@
         <v>45478</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45370</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>44957</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>44494</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>44974</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>46178</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>46178</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>46178</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>46178</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45771</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>46178</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47802,7 +47802,7 @@
         <v>46178</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>46178</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47948,7 +47948,7 @@
         <v>45637</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45593</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>46182</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>46182</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48245,7 +48245,7 @@
         <v>45126</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>45126</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>46182</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>45141</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>46155</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48615,7 +48615,7 @@
         <v>46185</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>46185</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45145</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48844,7 +48844,7 @@
         <v>45400</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>45403</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>44935</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>45114</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49151,7 +49151,7 @@
         <v>45114</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45706</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49297,7 +49297,7 @@
         <v>46188</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49375,7 +49375,7 @@
         <v>46188</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49453,7 +49453,7 @@
         <v>45546</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>45356</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>46181</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>45092</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45266</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45796</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45033</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>46196</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>44536</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50115,7 +50115,7 @@
         <v>46197</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>44596</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>46196</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50344,7 +50344,7 @@
         <v>46196</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>44573</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50490,7 +50490,7 @@
         <v>45796</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50563,7 +50563,7 @@
         <v>46196</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50641,7 +50641,7 @@
         <v>46196</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>46198</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50792,7 +50792,7 @@
         <v>46199</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>46199</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>46198</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51011,7 +51011,7 @@
         <v>46198</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51089,7 +51089,7 @@
         <v>45723</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>46199</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45550</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51313,7 +51313,7 @@
         <v>46199</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51386,7 +51386,7 @@
         <v>44641</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51459,7 +51459,7 @@
         <v>46202</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51532,7 +51532,7 @@
         <v>45881</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>45727</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51688,7 +51688,7 @@
         <v>45159</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51761,7 +51761,7 @@
         <v>46203</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45432</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51907,7 +51907,7 @@
         <v>46204</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>45883</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>45883</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         <v>45043</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>45183</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45183</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>45673</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52433,7 +52433,7 @@
         <v>45053</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45217</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45636</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>46206</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52725,7 +52725,7 @@
         <v>45313</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52803,7 +52803,7 @@
         <v>45121</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52881,7 +52881,7 @@
         <v>46206</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45205</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53027,7 +53027,7 @@
         <v>45205</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53100,7 +53100,7 @@
         <v>44679</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53178,7 +53178,7 @@
         <v>46213</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>46258</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>46213</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>45761</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>46043</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>44630</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45211</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>45798</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53787,7 +53787,7 @@
         <v>46258</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53865,7 +53865,7 @@
         <v>46213</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53943,7 +53943,7 @@
         <v>46043</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54016,7 +54016,7 @@
         <v>46258</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54094,7 +54094,7 @@
         <v>44651</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         <v>46258</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54245,7 +54245,7 @@
         <v>46258</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>45446</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>45446</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54469,7 +54469,7 @@
         <v>46260</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>46260</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>46217</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54703,7 +54703,7 @@
         <v>46216</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54781,7 +54781,7 @@
         <v>46217</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54859,7 +54859,7 @@
         <v>46218</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>45254</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55010,7 +55010,7 @@
         <v>45215</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55083,7 +55083,7 @@
         <v>45188</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55156,7 +55156,7 @@
         <v>45715</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45723</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45699</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55380,7 +55380,7 @@
         <v>46218</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55458,7 +55458,7 @@
         <v>45204</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>45468</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55609,7 +55609,7 @@
         <v>45401</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55687,7 +55687,7 @@
         <v>45274</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55760,7 +55760,7 @@
         <v>46178</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55833,7 +55833,7 @@
         <v>46265</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>45252</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55984,7 +55984,7 @@
         <v>45191</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>46265</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56135,7 +56135,7 @@
         <v>45758</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56213,7 +56213,7 @@
         <v>45254</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45246</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45246</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>44956</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>44956</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56593,7 +56593,7 @@
         <v>46225</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>45252</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45272</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56822,7 +56822,7 @@
         <v>46268</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45399</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>45317</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>46269</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57134,7 +57134,7 @@
         <v>44862</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57207,7 +57207,7 @@
         <v>45716</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57285,7 +57285,7 @@
         <v>45266</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57358,7 +57358,7 @@
         <v>46269</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57436,7 +57436,7 @@
         <v>44859</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>44469</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57587,7 +57587,7 @@
         <v>45330</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57660,7 +57660,7 @@
         <v>45266</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>44851</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57806,7 +57806,7 @@
         <v>46231</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57884,7 +57884,7 @@
         <v>45106</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57957,7 +57957,7 @@
         <v>45763</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58035,7 +58035,7 @@
         <v>45043</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58113,7 +58113,7 @@
         <v>46233</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58191,7 +58191,7 @@
         <v>46233</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58269,7 +58269,7 @@
         <v>44767</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>46233</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58420,7 +58420,7 @@
         <v>46233</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58498,7 +58498,7 @@
         <v>45268</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>46233</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58649,7 +58649,7 @@
         <v>44599</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58722,7 +58722,7 @@
         <v>46233</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58800,7 +58800,7 @@
         <v>44597</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58873,7 +58873,7 @@
         <v>46233</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58951,7 +58951,7 @@
         <v>46280</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59029,7 +59029,7 @@
         <v>46280</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59107,7 +59107,7 @@
         <v>46280</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59180,7 +59180,7 @@
         <v>45678</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59253,7 +59253,7 @@
         <v>44754</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59326,7 +59326,7 @@
         <v>46280</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59404,7 +59404,7 @@
         <v>44739</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59477,7 +59477,7 @@
         <v>44970</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59555,7 +59555,7 @@
         <v>46279</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59633,7 +59633,7 @@
         <v>46233</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>46233</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59789,7 +59789,7 @@
         <v>46233</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59867,7 +59867,7 @@
         <v>45215</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59940,7 +59940,7 @@
         <v>45106</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60013,7 +60013,7 @@
         <v>45053</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60086,7 +60086,7 @@
         <v>45733</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60164,7 +60164,7 @@
         <v>46241</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60237,7 +60237,7 @@
         <v>46241</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>46283</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60388,7 +60388,7 @@
         <v>44867</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>46282</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60544,7 +60544,7 @@
         <v>45043</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60617,7 +60617,7 @@
         <v>46286</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60690,7 +60690,7 @@
         <v>44861</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60768,7 +60768,7 @@
         <v>45008</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60841,7 +60841,7 @@
         <v>46288</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60919,7 +60919,7 @@
         <v>44936</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60997,7 +60997,7 @@
         <v>44936</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61075,7 +61075,7 @@
         <v>45030</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61148,7 +61148,7 @@
         <v>46244</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61221,7 +61221,7 @@
         <v>46288</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61299,7 +61299,7 @@
         <v>45174</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61372,7 +61372,7 @@
         <v>45174</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61445,7 +61445,7 @@
         <v>44992</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61518,7 +61518,7 @@
         <v>46244</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61596,7 +61596,7 @@
         <v>46244</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61669,7 +61669,7 @@
         <v>46244</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>46245</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61825,7 +61825,7 @@
         <v>46245</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61903,7 +61903,7 @@
         <v>45014</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61976,7 +61976,7 @@
         <v>46244</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62049,7 +62049,7 @@
         <v>46245</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62127,7 +62127,7 @@
         <v>46050</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62205,7 +62205,7 @@
         <v>45246</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62278,7 +62278,7 @@
         <v>45022</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>46289</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62424,7 +62424,7 @@
         <v>46240</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62497,7 +62497,7 @@
         <v>45090</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62575,7 +62575,7 @@
         <v>44783</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62648,7 +62648,7 @@
         <v>45356</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62721,7 +62721,7 @@
         <v>45043</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62794,7 +62794,7 @@
         <v>45699</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -62867,7 +62867,7 @@
         <v>45435</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62940,7 +62940,7 @@
         <v>45547</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63018,7 +63018,7 @@
         <v>45678</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>45086</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63169,7 +63169,7 @@
         <v>45636</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63242,7 +63242,7 @@
         <v>45071</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63315,7 +63315,7 @@
         <v>45096</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63393,7 +63393,7 @@
         <v>45583</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63471,7 +63471,7 @@
         <v>45153</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>45117</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63627,7 +63627,7 @@
         <v>45757</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63700,7 +63700,7 @@
         <v>45093</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63773,7 +63773,7 @@
         <v>44980</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63851,7 +63851,7 @@
         <v>44966</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63929,7 +63929,7 @@
         <v>45030</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -64002,7 +64002,7 @@
         <v>45478</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64080,7 +64080,7 @@
         <v>44977</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64158,7 +64158,7 @@
         <v>44644</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64236,7 +64236,7 @@
         <v>45012</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64309,7 +64309,7 @@
         <v>45076</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64387,7 +64387,7 @@
         <v>45706</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64460,7 +64460,7 @@
         <v>45048</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64533,7 +64533,7 @@
         <v>45121</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64611,7 +64611,7 @@
         <v>44803</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64684,7 +64684,7 @@
         <v>45769</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64762,7 +64762,7 @@
         <v>45628</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64840,7 +64840,7 @@
         <v>45436</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64918,7 +64918,7 @@
         <v>45758</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64991,7 +64991,7 @@
         <v>45092</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65064,7 +65064,7 @@
         <v>45535</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65137,7 +65137,7 @@
         <v>45373</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65210,7 +65210,7 @@
         <v>45219</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65283,7 +65283,7 @@
         <v>45330</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65356,7 +65356,7 @@
         <v>45386</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65434,7 +65434,7 @@
         <v>45723</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65507,7 +65507,7 @@
         <v>45027</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65580,7 +65580,7 @@
         <v>45373</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65653,7 +65653,7 @@
         <v>45558</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65726,7 +65726,7 @@
         <v>44935</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65804,7 +65804,7 @@
         <v>45478</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65882,7 +65882,7 @@
         <v>45118</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65955,7 +65955,7 @@
         <v>44980</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66033,7 +66033,7 @@
         <v>44977</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66111,7 +66111,7 @@
         <v>45678</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66184,7 +66184,7 @@
         <v>45153</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66262,7 +66262,7 @@
         <v>45603</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66335,7 +66335,7 @@
         <v>44936</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66408,7 +66408,7 @@
         <v>45742</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66481,7 +66481,7 @@
         <v>45153</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66559,7 +66559,7 @@
         <v>44907</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66632,7 +66632,7 @@
         <v>45211</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66705,7 +66705,7 @@
         <v>44936</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66778,7 +66778,7 @@
         <v>45016</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66856,7 +66856,7 @@
         <v>45129</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66929,7 +66929,7 @@
         <v>45457</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -67002,7 +67002,7 @@
         <v>45497</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67075,7 +67075,7 @@
         <v>45706</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67148,7 +67148,7 @@
         <v>45310</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67226,7 +67226,7 @@
         <v>45742</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67299,7 +67299,7 @@
         <v>45758</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67377,7 +67377,7 @@
         <v>45709</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67455,7 +67455,7 @@
         <v>45629</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67528,7 +67528,7 @@
         <v>45777</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67606,7 +67606,7 @@
         <v>45782</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67679,7 +67679,7 @@
         <v>45783</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67752,7 +67752,7 @@
         <v>45784</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67825,7 +67825,7 @@
         <v>45784</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67903,7 +67903,7 @@
         <v>45092</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67976,7 +67976,7 @@
         <v>45786</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -68054,7 +68054,7 @@
         <v>45671</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68127,7 +68127,7 @@
         <v>45453</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -68200,7 +68200,7 @@
         <v>45453</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -68273,7 +68273,7 @@
         <v>45786</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -68351,7 +68351,7 @@
         <v>44565</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -68429,7 +68429,7 @@
         <v>45310</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -68502,7 +68502,7 @@
         <v>45790</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -68575,7 +68575,7 @@
         <v>44313</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68648,7 +68648,7 @@
         <v>44130</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -68721,7 +68721,7 @@
         <v>44230</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -68794,7 +68794,7 @@
         <v>44638</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68872,7 +68872,7 @@
         <v>44649</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68950,7 +68950,7 @@
         <v>44551</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -69023,7 +69023,7 @@
         <v>44692</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -69096,7 +69096,7 @@
         <v>45316</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -69169,7 +69169,7 @@
         <v>45629</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -69242,7 +69242,7 @@
         <v>45571</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -69315,7 +69315,7 @@
         <v>45432</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -69388,7 +69388,7 @@
         <v>45571</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -69461,7 +69461,7 @@
         <v>45789</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -69534,7 +69534,7 @@
         <v>45784</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45798</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44896</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45723</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45723</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45723</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45917</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>46120</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45783</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>45579</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45922</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45645</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>45411</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45086</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45922</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>45817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>46120</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46146</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>45880</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>46120</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45441</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>45679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>45742</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>46195</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45723</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45441</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>45917</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45968</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>46048</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45917</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44578</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45964</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>46212</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>45048</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45336</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45782</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45789</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>45905</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>45884</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>46120</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>45833</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>45373</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>45042</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>45954</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>46218</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>45421</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>45604</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>44622</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>45733</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45579</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45133</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>46037</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45796</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45917</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>46135</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>46136</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>45860</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>44931</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44746</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45702</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>45013</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>46198</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>46213</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>44977</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>46268</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>45258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>45727</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>44981</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>45016</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44524</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>44557</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>44880</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45895</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>46043</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45742</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>45936</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45905</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>46086</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>45583</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44993</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45978</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>45985</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>44974</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>44789</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>45086</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>45334</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>45369</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45721</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45769</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>45716</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>44957</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45394</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>45694</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>46198</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>44886</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>46199</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>46199</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>45797</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>46218</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>46218</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>46219</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45056</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>46233</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>46233</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44742</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45201</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>46282</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45716</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>45414</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45758</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45763</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>45783</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>44915</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>45791</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>45918</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>44480</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44524</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>44813</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44490</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44475</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>45362</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44777</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>45583</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>45894</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45894</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>45702</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45905</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45904</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>46038</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45771</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>46055</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45174</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45363</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>44935</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45096</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>45744</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>46079</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>46084</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>45744</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45583</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44943</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45833</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45317</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>44504</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45845</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45645</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>46139</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45798</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45090</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45250</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45733</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44974</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>44897</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>46163</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45580</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>45008</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45117</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>46178</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44652</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45201</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>46202</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45096</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>46217</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>46218</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>46219</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45117</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>46225</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>46231</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>46233</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>46233</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>46241</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>45408</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>46288</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45043</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45924</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45376</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45405</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>45251</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45726</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>44596</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44529</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>44530</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44502</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>44537</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>44582</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>44825</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44739</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44719</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>44503</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44865</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>44524</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44696</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44494</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>44671</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44713</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44530</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>44515</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44571</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>44475</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>44475</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44630</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>44530</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>44503</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>44879</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>44475</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>44574</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>44889</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>44825</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44686</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>44602</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>44582</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>44825</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>44741</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44730</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>44578</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>44886</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>44740</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>44874</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>44726</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>44487</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>44596</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>44630</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44869</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45401</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44651</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>45106</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44957</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>45469</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>44900</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45118</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>44826</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>44783</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>45086</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45076</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44512</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>45706</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>45386</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45716</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>44935</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45093</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44861</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45110</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45053</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45356</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>44565</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45092</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44998</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45266</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45453</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45453</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45310</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>45887</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45092</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44974</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45636</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45313</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45238</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45887</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>44741</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>45742</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>46007</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>46006</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>46006</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>46007</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>46006</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>46006</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>46010</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>46010</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>45790</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>46010</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>46010</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>45386</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>45022</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27833,7 +27833,7 @@
         <v>45043</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45888</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>45888</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>44970</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44862</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>45895</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45895</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>45254</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45894</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45894</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45896</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>46030</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45583</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>45535</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45896</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>46010</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>46030</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45898</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>45817</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>45356</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45903</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44980</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>46035</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>45903</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>44956</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>44966</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>46037</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>46041</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44936</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>45908</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>45908</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>45246</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30264,7 +30264,7 @@
         <v>46038</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>44575</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>46042</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>46042</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>45414</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>46042</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>45259</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>45796</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45678</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>45796</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>46045</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
         <v>46048</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>45272</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45917</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>45798</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>45603</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45400</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>46046</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>46046</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>46048</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>45274</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>45917</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>45408</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>45565</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45798</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>45554</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44754</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>45722</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45803</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45762</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45804</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45174</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45174</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         <v>45922</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>45922</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>46052</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>46052</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33005,7 +33005,7 @@
         <v>45924</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>46052</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45924</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45924</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>45628</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45926</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>44897</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>45930</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44935</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44950</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>44896</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>44858</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>45436</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45758</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>44644</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>45936</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>45110</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45110</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45873</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>46072</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>45943</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45532</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>45202</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34754,7 +34754,7 @@
         <v>46072</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45121</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45597</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>46076</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>46076</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45071</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45678</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>44889</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45678</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45317</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>45202</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>45369</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>46079</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>45043</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>46079</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>45478</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45098</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45414</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>46090</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45183</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>45960</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>45960</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36400,7 +36400,7 @@
         <v>45764</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>45961</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36546,7 +36546,7 @@
         <v>45043</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>46072</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         <v>45757</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>46072</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>46093</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36916,7 +36916,7 @@
         <v>45240</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>45817</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>46093</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45118</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37213,7 +37213,7 @@
         <v>46094</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>46094</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>46093</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>46094</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>46093</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>45715</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>44536</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>45153</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45215</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>45096</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>44599</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44999</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>46101</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>45049</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45975</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45330</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>46101</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>45219</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>45468</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>46106</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>45201</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>45976</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>44980</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>46108</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>46107</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39098,7 +39098,7 @@
         <v>45985</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>45820</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>45985</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>45820</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>45986</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39478,7 +39478,7 @@
         <v>45986</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>45317</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>46120</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39707,7 +39707,7 @@
         <v>45365</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>46120</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45405</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>46120</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>45769</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>44923</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>45824</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>44930</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>45043</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>45092</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>44970</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>46128</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>44865</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         <v>44943</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45211</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>45211</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40905,7 +40905,7 @@
         <v>45833</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>46135</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>46135</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45215</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45891</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45832</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45657</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41426,7 +41426,7 @@
         <v>45436</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>45204</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45356</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>45215</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41728,7 +41728,7 @@
         <v>46139</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45884</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45141</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>44945</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45924</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>45833</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>44936</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>45840</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42322,7 +42322,7 @@
         <v>45006</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45845</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45582</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42556,7 +42556,7 @@
         <v>45678</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         <v>45886</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45966</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45889</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45796</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>45386</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>44825</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45520</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45736</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45891</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45030</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>44939</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45093</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45012</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>45153</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>45709</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>46139</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45867</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45836</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>44867</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45178</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45373</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>44980</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45016</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>45254</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>45742</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>46139</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45497</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>44861</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>44607</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45629</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45706</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>45716</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45106</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45706</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45769</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>45266</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45435</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>44977</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45709</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45114</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44630</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45008</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>44783</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>44977</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>44719</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45012</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>46146</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>46146</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45310</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46296,7 +46296,7 @@
         <v>45706</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46369,7 +46369,7 @@
         <v>45761</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46447,7 +46447,7 @@
         <v>45153</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45490</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45370</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>44805</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44907</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45117</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>45121</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>45733</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47061,7 +47061,7 @@
         <v>44767</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47134,7 +47134,7 @@
         <v>45072</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>45106</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47285,7 +47285,7 @@
         <v>44853</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>45369</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>45629</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45478</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>45727</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>45090</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>46163</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45758</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>44936</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45432</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45205</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>45889</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48181,7 +48181,7 @@
         <v>45446</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48254,7 +48254,7 @@
         <v>45446</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45629</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48400,7 +48400,7 @@
         <v>45077</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48473,7 +48473,7 @@
         <v>45092</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>45278</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>46061</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48692,7 +48692,7 @@
         <v>45796</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45030</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45399</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48916,7 +48916,7 @@
         <v>45547</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48994,7 +48994,7 @@
         <v>45159</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>45881</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>45121</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>45699</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45699</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>45883</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         <v>45883</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>44910</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49593,7 +49593,7 @@
         <v>44928</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45883</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>45637</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45117</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45883</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>46178</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>46178</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50119,7 +50119,7 @@
         <v>46178</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50192,7 +50192,7 @@
         <v>46178</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45678</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50338,7 +50338,7 @@
         <v>46178</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>46178</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45014</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>46178</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>46182</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45266</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50776,7 +50776,7 @@
         <v>45049</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50849,7 +50849,7 @@
         <v>45049</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45266</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         <v>46182</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>46182</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45237</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>44974</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>46155</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>46188</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>44965</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>46185</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>46188</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>46185</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51755,7 +51755,7 @@
         <v>44834</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>44596</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>46181</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51984,7 +51984,7 @@
         <v>45771</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>45546</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52135,7 +52135,7 @@
         <v>46196</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45229</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>45796</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52359,7 +52359,7 @@
         <v>46196</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52432,7 +52432,7 @@
         <v>45030</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>45030</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>46196</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52656,7 +52656,7 @@
         <v>46196</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         <v>46196</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>45188</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>46197</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>45268</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53026,7 +53026,7 @@
         <v>45550</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>46198</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>46198</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>46198</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53328,7 +53328,7 @@
         <v>45053</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>44860</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>46202</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>44597</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>46199</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>46199</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>45014</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53839,7 +53839,7 @@
         <v>44936</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>46199</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>46199</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54063,7 +54063,7 @@
         <v>45723</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>44588</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>46204</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>44641</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>46203</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54433,7 +54433,7 @@
         <v>46206</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54506,7 +54506,7 @@
         <v>44494</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54579,7 +54579,7 @@
         <v>46206</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54652,7 +54652,7 @@
         <v>45274</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54725,7 +54725,7 @@
         <v>45558</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>44859</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54876,7 +54876,7 @@
         <v>46213</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>46216</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55032,7 +55032,7 @@
         <v>45336</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>46258</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>44582</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55256,7 +55256,7 @@
         <v>45442</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55334,7 +55334,7 @@
         <v>46258</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55412,7 +55412,7 @@
         <v>45183</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55485,7 +55485,7 @@
         <v>45183</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55558,7 +55558,7 @@
         <v>46258</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55636,7 +55636,7 @@
         <v>45798</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55714,7 +55714,7 @@
         <v>45043</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55787,7 +55787,7 @@
         <v>46213</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55865,7 +55865,7 @@
         <v>46258</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>46258</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56021,7 +56021,7 @@
         <v>46213</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>45509</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56172,7 +56172,7 @@
         <v>46260</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>46218</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>45145</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56401,7 +56401,7 @@
         <v>46217</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56479,7 +56479,7 @@
         <v>46218</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56557,7 +56557,7 @@
         <v>46217</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56635,7 +56635,7 @@
         <v>46260</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45215</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56786,7 +56786,7 @@
         <v>46265</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56864,7 +56864,7 @@
         <v>46265</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>44936</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57015,7 +57015,7 @@
         <v>44890</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>45769</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57166,7 +57166,7 @@
         <v>45013</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57239,7 +57239,7 @@
         <v>44956</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>44721</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>46178</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57463,7 +57463,7 @@
         <v>45217</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57536,7 +57536,7 @@
         <v>45191</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>46269</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57687,7 +57687,7 @@
         <v>46268</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57765,7 +57765,7 @@
         <v>46269</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57843,7 +57843,7 @@
         <v>46225</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57921,7 +57921,7 @@
         <v>45733</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57999,7 +57999,7 @@
         <v>44803</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58072,7 +58072,7 @@
         <v>44860</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58145,7 +58145,7 @@
         <v>44939</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58223,7 +58223,7 @@
         <v>44956</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58301,7 +58301,7 @@
         <v>45379</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58374,7 +58374,7 @@
         <v>46231</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58452,7 +58452,7 @@
         <v>46233</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58530,7 +58530,7 @@
         <v>46233</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58608,7 +58608,7 @@
         <v>46279</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>46233</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>46233</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58842,7 +58842,7 @@
         <v>46233</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58920,7 +58920,7 @@
         <v>44677</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58993,7 +58993,7 @@
         <v>46233</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59071,7 +59071,7 @@
         <v>46280</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59149,7 +59149,7 @@
         <v>46280</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59227,7 +59227,7 @@
         <v>45126</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59300,7 +59300,7 @@
         <v>45126</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59373,7 +59373,7 @@
         <v>46280</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>46280</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59524,7 +59524,7 @@
         <v>45268</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         <v>44907</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59670,7 +59670,7 @@
         <v>45114</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59748,7 +59748,7 @@
         <v>45114</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59821,7 +59821,7 @@
         <v>45723</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59894,7 +59894,7 @@
         <v>46283</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59972,7 +59972,7 @@
         <v>44679</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60050,7 +60050,7 @@
         <v>46282</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60128,7 +60128,7 @@
         <v>45359</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60201,7 +60201,7 @@
         <v>46241</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60274,7 +60274,7 @@
         <v>44880</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60352,7 +60352,7 @@
         <v>46286</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60425,7 +60425,7 @@
         <v>46244</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60498,7 +60498,7 @@
         <v>46241</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60571,7 +60571,7 @@
         <v>46244</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60649,7 +60649,7 @@
         <v>46244</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>46244</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60800,7 +60800,7 @@
         <v>46244</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60873,7 +60873,7 @@
         <v>44936</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>44936</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61029,7 +61029,7 @@
         <v>45769</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>44488</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61175,7 +61175,7 @@
         <v>44994</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61248,7 +61248,7 @@
         <v>45028</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61321,7 +61321,7 @@
         <v>45442</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61394,7 +61394,7 @@
         <v>46289</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61467,7 +61467,7 @@
         <v>46288</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61545,7 +61545,7 @@
         <v>46245</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>45408</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>46245</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>45106</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>46050</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>46245</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -62003,7 +62003,7 @@
         <v>44862</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>46288</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62159,7 +62159,7 @@
         <v>44805</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>46052</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45201</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>45132</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62461,7 +62461,7 @@
         <v>45373</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62534,7 +62534,7 @@
         <v>44992</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>46293</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62685,7 +62685,7 @@
         <v>45252</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62758,7 +62758,7 @@
         <v>45369</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62831,7 +62831,7 @@
         <v>45673</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62904,7 +62904,7 @@
         <v>45128</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62977,7 +62977,7 @@
         <v>45741</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -63055,7 +63055,7 @@
         <v>45769</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -63133,7 +63133,7 @@
         <v>45096</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>45246</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63284,7 +63284,7 @@
         <v>45246</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63357,7 +63357,7 @@
         <v>45174</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63430,7 +63430,7 @@
         <v>45174</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63503,7 +63503,7 @@
         <v>45457</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63576,7 +63576,7 @@
         <v>45092</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63649,7 +63649,7 @@
         <v>45254</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63727,7 +63727,7 @@
         <v>45027</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63800,7 +63800,7 @@
         <v>45425</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63873,7 +63873,7 @@
         <v>45581</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63946,7 +63946,7 @@
         <v>45091</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -64024,7 +64024,7 @@
         <v>45369</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -64097,7 +64097,7 @@
         <v>46043</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -64170,7 +64170,7 @@
         <v>45043</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>45442</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64321,7 +64321,7 @@
         <v>45008</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64394,7 +64394,7 @@
         <v>45763</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64472,7 +64472,7 @@
         <v>45339</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64545,7 +64545,7 @@
         <v>46294</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64618,7 +64618,7 @@
         <v>46240</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64691,7 +64691,7 @@
         <v>45093</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64764,7 +64764,7 @@
         <v>44992</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64837,7 +64837,7 @@
         <v>44980</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64915,7 +64915,7 @@
         <v>45453</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64988,7 +64988,7 @@
         <v>45252</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -65061,7 +65061,7 @@
         <v>45636</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -65134,7 +65134,7 @@
         <v>45636</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65207,7 +65207,7 @@
         <v>44573</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65280,7 +65280,7 @@
         <v>45330</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65353,7 +65353,7 @@
         <v>44862</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65431,7 +65431,7 @@
         <v>44573</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65504,7 +65504,7 @@
         <v>45110</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65582,7 +65582,7 @@
         <v>44713</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65655,7 +65655,7 @@
         <v>45112</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65728,7 +65728,7 @@
         <v>45043</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65806,7 +65806,7 @@
         <v>44739</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65879,7 +65879,7 @@
         <v>45317</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65957,7 +65957,7 @@
         <v>45432</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -66030,7 +66030,7 @@
         <v>45715</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -66108,7 +66108,7 @@
         <v>45726</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66181,7 +66181,7 @@
         <v>45723</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66254,7 +66254,7 @@
         <v>45030</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66327,7 +66327,7 @@
         <v>45030</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66400,7 +66400,7 @@
         <v>45254</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66478,7 +66478,7 @@
         <v>45205</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66551,7 +66551,7 @@
         <v>44851</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>45129</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>45478</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66775,7 +66775,7 @@
         <v>44957</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66853,7 +66853,7 @@
         <v>45403</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66926,7 +66926,7 @@
         <v>45033</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66999,7 +66999,7 @@
         <v>45593</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -67077,7 +67077,7 @@
         <v>45037</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -67150,7 +67150,7 @@
         <v>45030</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67223,7 +67223,7 @@
         <v>45048</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67296,7 +67296,7 @@
         <v>45777</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67374,7 +67374,7 @@
         <v>45783</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67447,7 +67447,7 @@
         <v>45782</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67520,7 +67520,7 @@
         <v>45671</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67593,7 +67593,7 @@
         <v>45784</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67666,7 +67666,7 @@
         <v>45784</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67744,7 +67744,7 @@
         <v>45786</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67822,7 +67822,7 @@
         <v>45786</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67900,7 +67900,7 @@
         <v>44130</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67973,7 +67973,7 @@
         <v>44313</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -68046,7 +68046,7 @@
         <v>44230</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -68119,7 +68119,7 @@
         <v>45316</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -68192,7 +68192,7 @@
         <v>44638</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68270,7 +68270,7 @@
         <v>44649</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -68348,7 +68348,7 @@
         <v>44551</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -68421,7 +68421,7 @@
         <v>45629</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -68494,7 +68494,7 @@
         <v>45571</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -68567,7 +68567,7 @@
         <v>45432</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -68640,7 +68640,7 @@
         <v>44692</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -68713,7 +68713,7 @@
         <v>45571</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68786,7 +68786,7 @@
         <v>45789</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -68859,7 +68859,7 @@
         <v>45784</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45798</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44896</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45723</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45723</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45723</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45917</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>45579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>46120</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>45783</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>46280</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>45922</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45139</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45411</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45086</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>45922</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45817</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>45880</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>46120</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>46146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45441</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>46120</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>46283</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>45679</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45742</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>45441</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>45917</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>45968</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>45782</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45917</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>45336</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44578</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>45048</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>46043</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>46048</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45964</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>46212</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>45789</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45373</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>45905</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>45604</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45833</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>45042</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>46120</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45884</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>45954</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>46218</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>45421</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44622</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>45013</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>45258</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44977</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45917</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45796</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>44931</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>45727</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>45733</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45860</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>45702</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>44746</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45016</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>46136</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>46135</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>45133</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>46037</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>44981</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>46198</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>46213</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>46268</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>44524</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>44557</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45414</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45334</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>44789</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44886</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>45763</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45783</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45201</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45394</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45936</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45716</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45905</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44993</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45369</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>45716</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45769</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44742</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>45978</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>44880</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45742</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45758</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45985</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45583</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44957</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45056</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>45086</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45721</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>46086</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>46198</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>46199</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>46199</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45797</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>46218</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>46218</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>46219</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>46233</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>46233</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>46282</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>44915</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45791</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45918</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>44480</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44524</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>44813</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44490</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>45363</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>45090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>44652</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>45744</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45744</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45408</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45117</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44935</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45894</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45894</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45250</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45405</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45904</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45905</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45726</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45376</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45362</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45771</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>45201</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45096</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44943</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45251</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45317</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45583</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45008</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>45583</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>45580</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45833</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45645</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44504</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45096</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45117</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45845</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44974</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45798</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>44777</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>45702</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45043</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>44897</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45174</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>46038</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>46139</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>46055</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>46079</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>46084</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>46163</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>46178</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>46202</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>46217</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>46218</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>46219</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>46225</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>46231</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>46233</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>46233</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>46241</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>46288</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45924</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44596</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>44529</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>44530</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>44582</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44537</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>44502</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>44825</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44739</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>44719</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44503</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>44865</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44524</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>44696</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>44494</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>44713</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>44671</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>44530</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44515</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>44571</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>44630</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44530</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44503</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>44879</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44582</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>44825</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>44741</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>44740</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44730</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>44574</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>44686</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>44602</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>44578</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>44726</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>44889</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44825</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>44487</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>44886</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44596</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>44874</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>44630</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>44896</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>44869</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>44900</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45076</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>44805</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>45118</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45369</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>45336</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>45092</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45037</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>45769</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>45706</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44897</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>45709</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>44928</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>44923</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>45048</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45121</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45405</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>44907</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44803</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>44588</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45436</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45268</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45043</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45215</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44825</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>44862</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>44865</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44860</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>44783</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>45072</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45628</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45436</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>44862</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45716</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45386</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45043</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>45092</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>45202</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>45532</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45535</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45317</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45373</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45359</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45128</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44861</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45106</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45425</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>45379</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44880</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45317</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>45219</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45330</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45386</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45883</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45883</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>44939</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45278</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44858</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45723</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45339</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45408</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>45027</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45883</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45373</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>45558</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>44935</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45478</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45093</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>45883</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>45118</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44980</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>44977</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45254</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45678</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44488</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45153</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>45096</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45603</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>44607</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>44936</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45742</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45888</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45153</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>45887</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>45888</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45887</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>44950</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45092</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45006</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45266</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45490</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>44930</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>44907</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45030</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45030</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>45211</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>44936</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>44936</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>45016</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45129</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>44994</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45894</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>45896</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45896</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45895</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>45895</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>45457</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45898</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>45497</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>45706</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45310</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>44890</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>45742</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>45817</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>45110</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45110</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45758</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45903</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45709</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>45414</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>45903</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32919,7 +32919,7 @@
         <v>45629</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>45908</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45908</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>45478</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45370</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>44957</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>44494</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>44974</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>44582</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>45771</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45777</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45782</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45637</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45593</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45783</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>45126</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>45126</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>45784</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45784</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45202</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45141</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>45365</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>45917</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45145</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45400</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45442</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44936</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>45092</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45917</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>45403</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>44935</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>45786</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>45671</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>45114</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35486,7 +35486,7 @@
         <v>45114</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45030</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>45922</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>45922</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44889</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45028</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>45453</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44910</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>45453</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>45924</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45546</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>45356</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45924</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45786</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>44565</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>45310</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36679,7 +36679,7 @@
         <v>45924</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45790</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45092</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45106</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45926</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45266</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>45930</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45201</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37268,7 +37268,7 @@
         <v>45033</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44536</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45678</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>44596</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44573</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
         <v>45796</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45369</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37784,7 +37784,7 @@
         <v>45215</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>45678</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>44936</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>45796</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45259</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38154,7 +38154,7 @@
         <v>44974</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>45550</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>45798</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>44943</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>45798</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45174</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38607,7 +38607,7 @@
         <v>45174</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45727</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>45565</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>45159</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>45408</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45432</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45554</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45936</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>45722</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>45043</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45803</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45804</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>45453</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45873</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>45762</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45238</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>45183</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39873,7 +39873,7 @@
         <v>45183</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45673</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45053</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>45217</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>45636</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>45313</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>45049</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>45121</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45369</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>45091</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>45112</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>44677</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>45943</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>45205</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>45205</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>44834</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>44679</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41144,7 +41144,7 @@
         <v>44741</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45817</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>45761</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45820</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>44630</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41519,7 +41519,7 @@
         <v>45211</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45820</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41665,7 +41665,7 @@
         <v>44965</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45014</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>45824</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41889,7 +41889,7 @@
         <v>44956</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>45356</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>44651</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>45636</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>44719</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>45581</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45446</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45446</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>44573</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>45414</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>45960</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45960</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45832</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45961</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42926,7 +42926,7 @@
         <v>45254</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>45215</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43072,7 +43072,7 @@
         <v>45833</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>44998</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>44512</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43296,7 +43296,7 @@
         <v>45188</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43369,7 +43369,7 @@
         <v>44970</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43442,7 +43442,7 @@
         <v>45715</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45723</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>44980</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45699</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45840</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45386</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>44721</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45114</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45204</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45468</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45401</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45678</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45274</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45629</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45098</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>44805</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>45117</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45582</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45845</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45597</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>45252</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45469</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45726</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45191</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>44713</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45758</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45254</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>45121</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45736</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>45246</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45246</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>45201</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45030</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45030</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>44956</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>44956</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>44853</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>45252</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45272</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44999</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45110</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45399</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>44826</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45442</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45317</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45706</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45975</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46968,7 +46968,7 @@
         <v>45442</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45976</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>44862</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>45716</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45008</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>44980</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>45266</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45013</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>44859</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>45330</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>45229</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45266</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>44851</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>45764</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>45106</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>45715</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>44992</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45796</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45043</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>44575</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>44957</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>44945</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>45093</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>45110</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45274</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>44767</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>45881</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>46094</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>45268</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49140,7 +49140,7 @@
         <v>44599</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>44597</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
         <v>45254</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49364,7 +49364,7 @@
         <v>45077</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>45509</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49510,7 +49510,7 @@
         <v>46101</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45678</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>46101</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>44754</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>44739</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49885,7 +49885,7 @@
         <v>45043</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>45986</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>44970</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50114,7 +50114,7 @@
         <v>45183</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>45215</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45106</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45985</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45986</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>46107</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45049</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50640,7 +50640,7 @@
         <v>45049</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45985</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>44939</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45012</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50937,7 +50937,7 @@
         <v>45053</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51010,7 +51010,7 @@
         <v>45237</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>45769</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51166,7 +51166,7 @@
         <v>46106</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51244,7 +51244,7 @@
         <v>45769</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51317,7 +51317,7 @@
         <v>46108</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51390,7 +51390,7 @@
         <v>45769</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51463,7 +51463,7 @@
         <v>45733</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51541,7 +51541,7 @@
         <v>44860</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51614,7 +51614,7 @@
         <v>45741</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51692,7 +51692,7 @@
         <v>45733</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>46120</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51843,7 +51843,7 @@
         <v>46120</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51921,7 +51921,7 @@
         <v>46120</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51994,7 +51994,7 @@
         <v>44867</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         <v>45043</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52145,7 +52145,7 @@
         <v>44861</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45008</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>44936</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>44936</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>45030</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>46128</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>45174</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>45174</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>44992</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>46006</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>46006</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>46006</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45014</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>46006</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53202,7 +53202,7 @@
         <v>45246</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>45836</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45884</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53426,7 +53426,7 @@
         <v>45889</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53499,7 +53499,7 @@
         <v>45924</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>46007</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53650,7 +53650,7 @@
         <v>46135</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>46135</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53801,7 +53801,7 @@
         <v>45022</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53874,7 +53874,7 @@
         <v>45657</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>46007</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>45833</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54103,7 +54103,7 @@
         <v>45090</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>45966</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>46010</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>44783</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54400,7 +54400,7 @@
         <v>46010</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54473,7 +54473,7 @@
         <v>46010</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54546,7 +54546,7 @@
         <v>45891</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54619,7 +54619,7 @@
         <v>45891</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54692,7 +54692,7 @@
         <v>45520</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>46010</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54838,7 +54838,7 @@
         <v>45356</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54911,7 +54911,7 @@
         <v>45043</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54984,7 +54984,7 @@
         <v>46139</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55057,7 +55057,7 @@
         <v>45886</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55130,7 +55130,7 @@
         <v>46010</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45178</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>46030</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45699</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>46030</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>45435</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55578,7 +55578,7 @@
         <v>45547</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55656,7 +55656,7 @@
         <v>45086</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>45636</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55807,7 +55807,7 @@
         <v>46035</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55885,7 +55885,7 @@
         <v>45071</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55958,7 +55958,7 @@
         <v>45796</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56031,7 +56031,7 @@
         <v>46038</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>46037</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56182,7 +56182,7 @@
         <v>46042</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56255,7 +56255,7 @@
         <v>46042</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>45096</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>46042</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56479,7 +56479,7 @@
         <v>46041</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56557,7 +56557,7 @@
         <v>45583</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56635,7 +56635,7 @@
         <v>45153</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45117</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45757</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56864,7 +56864,7 @@
         <v>46139</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45093</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57015,7 +57015,7 @@
         <v>46139</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57088,7 +57088,7 @@
         <v>45867</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57161,7 +57161,7 @@
         <v>44980</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57239,7 +57239,7 @@
         <v>44966</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>45030</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45478</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57468,7 +57468,7 @@
         <v>44977</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57546,7 +57546,7 @@
         <v>46046</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>46048</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>46048</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57770,7 +57770,7 @@
         <v>46046</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57843,7 +57843,7 @@
         <v>46045</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>44644</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57994,7 +57994,7 @@
         <v>45012</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58067,7 +58067,7 @@
         <v>46052</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58140,7 +58140,7 @@
         <v>46052</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58213,7 +58213,7 @@
         <v>46052</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>46146</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58364,7 +58364,7 @@
         <v>46146</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58442,7 +58442,7 @@
         <v>46072</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58520,7 +58520,7 @@
         <v>46076</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>46076</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58666,7 +58666,7 @@
         <v>46079</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58739,7 +58739,7 @@
         <v>46072</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58812,7 +58812,7 @@
         <v>46072</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58885,7 +58885,7 @@
         <v>46090</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58963,7 +58963,7 @@
         <v>46093</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>46093</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59109,7 +59109,7 @@
         <v>46093</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59182,7 +59182,7 @@
         <v>46093</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>46094</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59333,7 +59333,7 @@
         <v>46094</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45369</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59484,7 +59484,7 @@
         <v>46163</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59557,7 +59557,7 @@
         <v>45629</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59630,7 +59630,7 @@
         <v>46061</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59703,7 +59703,7 @@
         <v>45432</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59776,7 +59776,7 @@
         <v>45889</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59849,7 +59849,7 @@
         <v>46178</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>46178</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59995,7 +59995,7 @@
         <v>46178</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60068,7 +60068,7 @@
         <v>46178</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60141,7 +60141,7 @@
         <v>46178</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60214,7 +60214,7 @@
         <v>46178</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60287,7 +60287,7 @@
         <v>46178</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60360,7 +60360,7 @@
         <v>46182</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>46182</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60506,7 +60506,7 @@
         <v>46182</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>46155</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60652,7 +60652,7 @@
         <v>46185</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         <v>46185</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60808,7 +60808,7 @@
         <v>46188</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60886,7 +60886,7 @@
         <v>46188</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60964,7 +60964,7 @@
         <v>46181</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61037,7 +61037,7 @@
         <v>45796</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61115,7 +61115,7 @@
         <v>46196</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61188,7 +61188,7 @@
         <v>46196</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61261,7 +61261,7 @@
         <v>46196</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61334,7 +61334,7 @@
         <v>46196</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>46196</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61485,7 +61485,7 @@
         <v>46198</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61563,7 +61563,7 @@
         <v>46199</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61636,7 +61636,7 @@
         <v>46199</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61709,7 +61709,7 @@
         <v>46198</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>46198</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61860,7 +61860,7 @@
         <v>46199</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61938,7 +61938,7 @@
         <v>46199</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62011,7 +62011,7 @@
         <v>44641</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62084,7 +62084,7 @@
         <v>46202</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62157,7 +62157,7 @@
         <v>46203</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>46204</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62308,7 +62308,7 @@
         <v>46206</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62381,7 +62381,7 @@
         <v>46206</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>46213</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62532,7 +62532,7 @@
         <v>46213</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62610,7 +62610,7 @@
         <v>45798</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62688,7 +62688,7 @@
         <v>46213</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62766,7 +62766,7 @@
         <v>46217</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62844,7 +62844,7 @@
         <v>46216</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -62922,7 +62922,7 @@
         <v>46217</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -63000,7 +63000,7 @@
         <v>46218</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63078,7 +63078,7 @@
         <v>46218</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63156,7 +63156,7 @@
         <v>46178</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63229,7 +63229,7 @@
         <v>46265</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63307,7 +63307,7 @@
         <v>46265</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63385,7 +63385,7 @@
         <v>46225</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63463,7 +63463,7 @@
         <v>46268</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63541,7 +63541,7 @@
         <v>46269</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>46269</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63697,7 +63697,7 @@
         <v>46231</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63775,7 +63775,7 @@
         <v>46233</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>46233</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63931,7 +63931,7 @@
         <v>46233</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>46233</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -64087,7 +64087,7 @@
         <v>46280</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64165,7 +64165,7 @@
         <v>46280</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>46280</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64321,7 +64321,7 @@
         <v>46279</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64399,7 +64399,7 @@
         <v>46233</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>46233</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         <v>46241</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64628,7 +64628,7 @@
         <v>46241</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64701,7 +64701,7 @@
         <v>46282</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
         <v>46288</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64857,7 +64857,7 @@
         <v>46244</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64930,7 +64930,7 @@
         <v>46288</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -65008,7 +65008,7 @@
         <v>46244</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -65086,7 +65086,7 @@
         <v>46244</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>46244</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>46245</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65315,7 +65315,7 @@
         <v>46245</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65393,7 +65393,7 @@
         <v>46244</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65466,7 +65466,7 @@
         <v>46245</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65544,7 +65544,7 @@
         <v>46050</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65622,7 +65622,7 @@
         <v>46289</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65695,7 +65695,7 @@
         <v>46052</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65768,7 +65768,7 @@
         <v>46293</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65846,7 +65846,7 @@
         <v>46294</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65919,7 +65919,7 @@
         <v>46043</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65992,7 +65992,7 @@
         <v>46072</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -66070,7 +66070,7 @@
         <v>45763</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66148,7 +66148,7 @@
         <v>46240</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66221,7 +66221,7 @@
         <v>46286</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66294,7 +66294,7 @@
         <v>46258</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66372,7 +66372,7 @@
         <v>46258</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66450,7 +66450,7 @@
         <v>46258</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66528,7 +66528,7 @@
         <v>46258</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66606,7 +66606,7 @@
         <v>46258</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66684,7 +66684,7 @@
         <v>46260</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66762,7 +66762,7 @@
         <v>46260</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66840,7 +66840,7 @@
         <v>45723</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66913,7 +66913,7 @@
         <v>45769</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66991,7 +66991,7 @@
         <v>44313</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -67064,7 +67064,7 @@
         <v>44130</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -67137,7 +67137,7 @@
         <v>44230</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67210,7 +67210,7 @@
         <v>44638</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67288,7 +67288,7 @@
         <v>44649</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67366,7 +67366,7 @@
         <v>44551</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67439,7 +67439,7 @@
         <v>44692</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67512,7 +67512,7 @@
         <v>45316</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67585,7 +67585,7 @@
         <v>45629</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67658,7 +67658,7 @@
         <v>45571</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67731,7 +67731,7 @@
         <v>45432</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67804,7 +67804,7 @@
         <v>45571</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67877,7 +67877,7 @@
         <v>45789</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67950,7 +67950,7 @@
         <v>45784</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45798</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44896</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45723</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45723</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45723</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45917</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>45579</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>46120</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>45783</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>46280</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>45922</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45139</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45411</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45086</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>45922</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45817</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>45880</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>46120</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>46146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45441</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>46120</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>46283</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>45679</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45742</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>45441</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>45917</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>45968</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>45782</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45917</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>45336</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44578</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>45048</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>46043</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>46048</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>45964</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>46212</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>45789</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45373</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>45905</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>45604</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45833</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>45042</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>46120</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45884</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>45954</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>46218</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>45421</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44622</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>45013</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>45258</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>44977</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45917</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45796</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>44931</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>45727</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>45733</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45860</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>45702</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>44746</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45016</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>46136</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>46135</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>45133</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>46037</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>44981</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>46198</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>46213</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>46268</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>44524</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>44557</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45414</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45334</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>44789</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44886</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>45763</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45783</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45201</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45394</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45936</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45716</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45905</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44993</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45369</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>45716</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45769</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44742</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>45694</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>45978</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>44880</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45742</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45758</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45985</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45583</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44957</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45056</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>45086</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45721</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>46086</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>46198</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>46199</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>46199</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45797</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>46218</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>46218</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>46219</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>46233</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>46233</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>46282</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>44915</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45791</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45918</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>44480</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44524</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>44813</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44490</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>45363</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>45090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>44652</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>45744</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45744</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45408</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45117</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44935</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45894</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45894</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45250</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45405</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45904</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45905</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45726</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45376</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45362</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45771</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>45201</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45096</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44943</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45251</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45317</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45583</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45008</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>45583</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>45580</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45833</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45645</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44504</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45096</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45117</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45845</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44974</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45798</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>44777</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>45702</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45043</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>44897</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45174</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>46038</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>46139</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>46055</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>46079</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>46084</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>46163</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>46178</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>46202</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>46217</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>46218</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>46219</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>46225</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>46231</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>46233</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>46233</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>46241</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>46288</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45924</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44596</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>44529</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>44530</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>44582</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44537</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>44502</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>44825</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44739</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>44719</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44503</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>44865</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44524</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>44696</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>44494</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>44713</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>44671</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>44530</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>44515</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>44571</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>44630</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44530</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44503</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>44879</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44582</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>44825</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>44741</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>44740</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44730</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>44574</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>44686</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>44602</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>44578</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>44726</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>44889</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44825</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>44487</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>44886</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44596</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>44874</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>44630</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>44896</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>44869</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>44900</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45076</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>44805</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>45118</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45369</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>45336</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>45092</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45037</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>45769</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>45706</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44897</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>45709</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>44928</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>44923</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>45048</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45121</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45405</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>44907</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44803</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>44588</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45436</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45268</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45043</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45215</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>44825</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>44862</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>44865</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44860</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>44783</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>45072</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45628</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45436</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>44862</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45716</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45386</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45043</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>45092</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>45202</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>45532</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45535</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45317</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45373</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45359</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45128</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44861</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45106</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45425</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>45379</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44880</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45317</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>45219</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45330</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45386</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45883</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45883</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>44939</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45278</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44858</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45723</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45339</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45408</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>45027</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45883</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45373</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>45558</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>44935</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45478</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45093</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>45883</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>45118</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44980</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>44977</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45254</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45678</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44488</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45153</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>45096</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45603</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>44607</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>44936</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45742</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45888</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45153</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>45887</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>45888</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45887</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>44950</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45092</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>45006</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45266</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45490</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>44930</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>44907</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45030</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45030</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>45211</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>44936</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>44936</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>45016</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45129</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>44994</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45894</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>45896</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45896</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45895</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>45895</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>45457</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45898</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>45497</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>45706</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45310</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>44890</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>45742</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>45817</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>45110</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45110</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45758</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45903</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45709</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>45414</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>45903</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32919,7 +32919,7 @@
         <v>45629</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>45908</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45908</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>45478</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45370</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>44957</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>44494</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>44974</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>44582</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>45771</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45777</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45782</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45637</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45593</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45783</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>45126</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>45126</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>45784</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45784</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45202</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45141</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>45365</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>45917</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45145</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45400</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45442</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44936</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>45092</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45917</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>45403</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>44935</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>45786</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>45671</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>45114</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35486,7 +35486,7 @@
         <v>45114</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45030</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>45922</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>45922</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44889</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45028</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>45453</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44910</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>45453</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>45924</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45546</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>45356</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45924</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45786</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>44565</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>45310</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36679,7 +36679,7 @@
         <v>45924</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45790</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45092</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45106</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45926</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45266</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>45930</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45201</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37268,7 +37268,7 @@
         <v>45033</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44536</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45678</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>44596</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44573</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
         <v>45796</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45369</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37784,7 +37784,7 @@
         <v>45215</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>45678</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>44936</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>45796</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45259</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38154,7 +38154,7 @@
         <v>44974</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>45550</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>45798</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>44943</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>45798</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45174</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38607,7 +38607,7 @@
         <v>45174</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45727</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>45565</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>45159</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>45408</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45432</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45554</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45936</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>45722</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>45043</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45803</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45804</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>45453</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45873</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>45762</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45238</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>45183</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39873,7 +39873,7 @@
         <v>45183</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45673</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45053</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>45217</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>45636</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>45313</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>45049</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>45121</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45369</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>45091</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>45112</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>44677</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>45943</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>45205</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>45205</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>44834</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>44679</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41144,7 +41144,7 @@
         <v>44741</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45817</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>45761</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45820</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>44630</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41519,7 +41519,7 @@
         <v>45211</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45820</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41665,7 +41665,7 @@
         <v>44965</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45014</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>45824</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41889,7 +41889,7 @@
         <v>44956</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>45356</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>44651</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>45636</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>44719</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>45581</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45446</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45446</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>44573</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>45414</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>45960</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45960</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45832</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45961</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42926,7 +42926,7 @@
         <v>45254</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>45215</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43072,7 +43072,7 @@
         <v>45833</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>44998</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>44512</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43296,7 +43296,7 @@
         <v>45188</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43369,7 +43369,7 @@
         <v>44970</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43442,7 +43442,7 @@
         <v>45715</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45723</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>44980</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45699</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45840</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45386</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>44721</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45114</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45204</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45468</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45401</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45678</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45274</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45629</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45098</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>44805</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>45117</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45582</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45845</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45597</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>45252</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45469</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45726</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45191</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>44713</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45758</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45254</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>45121</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45736</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>45246</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45246</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>45201</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45030</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45030</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>44956</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>44956</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>44853</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>45252</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45272</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44999</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45110</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45399</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>44826</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45442</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45317</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45706</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45975</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46968,7 +46968,7 @@
         <v>45442</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45976</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>44862</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>45716</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45008</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>44980</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>45266</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45013</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>44859</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>45330</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>45229</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45266</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>44851</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>45764</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>45106</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>45715</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>44992</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45796</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45043</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>44575</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>44957</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>44945</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>45093</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>45110</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>45274</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>44767</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>45881</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>46094</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>45268</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49140,7 +49140,7 @@
         <v>44599</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>44597</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
         <v>45254</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49364,7 +49364,7 @@
         <v>45077</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>45509</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49510,7 +49510,7 @@
         <v>46101</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45678</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>46101</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>44754</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>44739</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49885,7 +49885,7 @@
         <v>45043</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>45986</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>44970</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50114,7 +50114,7 @@
         <v>45183</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>45215</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45106</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45985</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45986</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>46107</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45049</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50640,7 +50640,7 @@
         <v>45049</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45985</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>44939</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45012</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50937,7 +50937,7 @@
         <v>45053</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51010,7 +51010,7 @@
         <v>45237</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>45769</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51166,7 +51166,7 @@
         <v>46106</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51244,7 +51244,7 @@
         <v>45769</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51317,7 +51317,7 @@
         <v>46108</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51390,7 +51390,7 @@
         <v>45769</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51463,7 +51463,7 @@
         <v>45733</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51541,7 +51541,7 @@
         <v>44860</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51614,7 +51614,7 @@
         <v>45741</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51692,7 +51692,7 @@
         <v>45733</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>46120</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51843,7 +51843,7 @@
         <v>46120</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51921,7 +51921,7 @@
         <v>46120</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51994,7 +51994,7 @@
         <v>44867</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         <v>45043</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52145,7 +52145,7 @@
         <v>44861</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45008</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>44936</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>44936</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>45030</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>46128</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>45174</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>45174</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>44992</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>46006</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>46006</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>46006</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45014</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>46006</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53202,7 +53202,7 @@
         <v>45246</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>45836</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45884</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53426,7 +53426,7 @@
         <v>45889</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53499,7 +53499,7 @@
         <v>45924</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>46007</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53650,7 +53650,7 @@
         <v>46135</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>46135</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53801,7 +53801,7 @@
         <v>45022</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53874,7 +53874,7 @@
         <v>45657</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>46007</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>45833</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54103,7 +54103,7 @@
         <v>45090</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>45966</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>46010</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>44783</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54400,7 +54400,7 @@
         <v>46010</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54473,7 +54473,7 @@
         <v>46010</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54546,7 +54546,7 @@
         <v>45891</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54619,7 +54619,7 @@
         <v>45891</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54692,7 +54692,7 @@
         <v>45520</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>46010</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54838,7 +54838,7 @@
         <v>45356</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54911,7 +54911,7 @@
         <v>45043</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54984,7 +54984,7 @@
         <v>46139</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55057,7 +55057,7 @@
         <v>45886</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55130,7 +55130,7 @@
         <v>46010</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45178</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>46030</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45699</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>46030</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>45435</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55578,7 +55578,7 @@
         <v>45547</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55656,7 +55656,7 @@
         <v>45086</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>45636</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55807,7 +55807,7 @@
         <v>46035</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55885,7 +55885,7 @@
         <v>45071</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55958,7 +55958,7 @@
         <v>45796</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56031,7 +56031,7 @@
         <v>46038</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>46037</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56182,7 +56182,7 @@
         <v>46042</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56255,7 +56255,7 @@
         <v>46042</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>45096</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>46042</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56479,7 +56479,7 @@
         <v>46041</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56557,7 +56557,7 @@
         <v>45583</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56635,7 +56635,7 @@
         <v>45153</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>45117</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45757</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56864,7 +56864,7 @@
         <v>46139</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45093</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57015,7 +57015,7 @@
         <v>46139</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57088,7 +57088,7 @@
         <v>45867</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57161,7 +57161,7 @@
         <v>44980</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57239,7 +57239,7 @@
         <v>44966</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>45030</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45478</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57468,7 +57468,7 @@
         <v>44977</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57546,7 +57546,7 @@
         <v>46046</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>46048</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>46048</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57770,7 +57770,7 @@
         <v>46046</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57843,7 +57843,7 @@
         <v>46045</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>44644</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57994,7 +57994,7 @@
         <v>45012</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58067,7 +58067,7 @@
         <v>46052</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58140,7 +58140,7 @@
         <v>46052</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58213,7 +58213,7 @@
         <v>46052</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>46146</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58364,7 +58364,7 @@
         <v>46146</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58442,7 +58442,7 @@
         <v>46072</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58520,7 +58520,7 @@
         <v>46076</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>46076</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58666,7 +58666,7 @@
         <v>46079</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58739,7 +58739,7 @@
         <v>46072</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58812,7 +58812,7 @@
         <v>46072</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58885,7 +58885,7 @@
         <v>46090</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58963,7 +58963,7 @@
         <v>46093</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>46093</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59109,7 +59109,7 @@
         <v>46093</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59182,7 +59182,7 @@
         <v>46093</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>46094</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59333,7 +59333,7 @@
         <v>46094</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45369</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59484,7 +59484,7 @@
         <v>46163</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59557,7 +59557,7 @@
         <v>45629</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59630,7 +59630,7 @@
         <v>46061</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59703,7 +59703,7 @@
         <v>45432</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59776,7 +59776,7 @@
         <v>45889</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59849,7 +59849,7 @@
         <v>46178</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>46178</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59995,7 +59995,7 @@
         <v>46178</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60068,7 +60068,7 @@
         <v>46178</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60141,7 +60141,7 @@
         <v>46178</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60214,7 +60214,7 @@
         <v>46178</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60287,7 +60287,7 @@
         <v>46178</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60360,7 +60360,7 @@
         <v>46182</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>46182</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60506,7 +60506,7 @@
         <v>46182</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>46155</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60652,7 +60652,7 @@
         <v>46185</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         <v>46185</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60808,7 +60808,7 @@
         <v>46188</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60886,7 +60886,7 @@
         <v>46188</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60964,7 +60964,7 @@
         <v>46181</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61037,7 +61037,7 @@
         <v>45796</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61115,7 +61115,7 @@
         <v>46196</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61188,7 +61188,7 @@
         <v>46196</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61261,7 +61261,7 @@
         <v>46196</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61334,7 +61334,7 @@
         <v>46196</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>46196</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61485,7 +61485,7 @@
         <v>46198</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61563,7 +61563,7 @@
         <v>46199</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61636,7 +61636,7 @@
         <v>46199</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61709,7 +61709,7 @@
         <v>46198</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>46198</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61860,7 +61860,7 @@
         <v>46199</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61938,7 +61938,7 @@
         <v>46199</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62011,7 +62011,7 @@
         <v>44641</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62084,7 +62084,7 @@
         <v>46202</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62157,7 +62157,7 @@
         <v>46203</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>46204</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62308,7 +62308,7 @@
         <v>46206</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62381,7 +62381,7 @@
         <v>46206</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>46213</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62532,7 +62532,7 @@
         <v>46213</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62610,7 +62610,7 @@
         <v>45798</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62688,7 +62688,7 @@
         <v>46213</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62766,7 +62766,7 @@
         <v>46217</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62844,7 +62844,7 @@
         <v>46216</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -62922,7 +62922,7 @@
         <v>46217</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -63000,7 +63000,7 @@
         <v>46218</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63078,7 +63078,7 @@
         <v>46218</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63156,7 +63156,7 @@
         <v>46178</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63229,7 +63229,7 @@
         <v>46265</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63307,7 +63307,7 @@
         <v>46265</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63385,7 +63385,7 @@
         <v>46225</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63463,7 +63463,7 @@
         <v>46268</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63541,7 +63541,7 @@
         <v>46269</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>46269</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63697,7 +63697,7 @@
         <v>46231</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63775,7 +63775,7 @@
         <v>46233</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>46233</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63931,7 +63931,7 @@
         <v>46233</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>46233</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -64087,7 +64087,7 @@
         <v>46280</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64165,7 +64165,7 @@
         <v>46280</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>46280</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64321,7 +64321,7 @@
         <v>46279</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64399,7 +64399,7 @@
         <v>46233</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>46233</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         <v>46241</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64628,7 +64628,7 @@
         <v>46241</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64701,7 +64701,7 @@
         <v>46282</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
         <v>46288</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64857,7 +64857,7 @@
         <v>46244</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64930,7 +64930,7 @@
         <v>46288</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -65008,7 +65008,7 @@
         <v>46244</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -65086,7 +65086,7 @@
         <v>46244</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>46244</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>46245</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65315,7 +65315,7 @@
         <v>46245</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65393,7 +65393,7 @@
         <v>46244</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65466,7 +65466,7 @@
         <v>46245</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65544,7 +65544,7 @@
         <v>46050</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65622,7 +65622,7 @@
         <v>46289</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65695,7 +65695,7 @@
         <v>46052</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65768,7 +65768,7 @@
         <v>46293</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65846,7 +65846,7 @@
         <v>46294</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65919,7 +65919,7 @@
         <v>46043</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65992,7 +65992,7 @@
         <v>46072</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -66070,7 +66070,7 @@
         <v>45763</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66148,7 +66148,7 @@
         <v>46240</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66221,7 +66221,7 @@
         <v>46286</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66294,7 +66294,7 @@
         <v>46258</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66372,7 +66372,7 @@
         <v>46258</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66450,7 +66450,7 @@
         <v>46258</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66528,7 +66528,7 @@
         <v>46258</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66606,7 +66606,7 @@
         <v>46258</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66684,7 +66684,7 @@
         <v>46260</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66762,7 +66762,7 @@
         <v>46260</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66840,7 +66840,7 @@
         <v>45723</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66913,7 +66913,7 @@
         <v>45769</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66991,7 +66991,7 @@
         <v>44313</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -67064,7 +67064,7 @@
         <v>44130</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -67137,7 +67137,7 @@
         <v>44230</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67210,7 +67210,7 @@
         <v>44638</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67288,7 +67288,7 @@
         <v>44649</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67366,7 +67366,7 @@
         <v>44551</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67439,7 +67439,7 @@
         <v>44692</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67512,7 +67512,7 @@
         <v>45316</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67585,7 +67585,7 @@
         <v>45629</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67658,7 +67658,7 @@
         <v>45571</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67731,7 +67731,7 @@
         <v>45432</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67804,7 +67804,7 @@
         <v>45571</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67877,7 +67877,7 @@
         <v>45789</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67950,7 +67950,7 @@
         <v>45784</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45798</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44896</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45723</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45723</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45723</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45917</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>46120</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45579</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46280</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45783</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>45922</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45139</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45411</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45086</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>45922</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>46146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>46120</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45817</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45880</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45441</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>46120</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>46283</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>45679</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45742</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>46269</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45441</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>45917</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45968</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45917</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44578</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>45964</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>46043</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>46048</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>46212</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45048</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>45336</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45782</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45789</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>45905</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>45373</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>45042</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>45884</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>46120</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45954</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>46218</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45604</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45421</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>46269</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>45833</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44622</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>45733</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>46136</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>45917</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44931</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>44746</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>45133</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>45702</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>46037</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>45013</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44977</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>46198</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>46135</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>45258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>46213</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45727</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44981</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>45016</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>46268</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>45860</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>44524</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>44557</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>44880</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45742</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45583</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>44993</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44974</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>44789</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45895</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>45086</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45334</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45936</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>45905</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>45769</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45978</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>45716</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>45985</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44957</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>45394</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>45694</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44886</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>46086</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>46198</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>46199</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>46199</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45056</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>44742</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>45201</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45797</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>46218</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>46218</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>46219</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45716</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>46233</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>46233</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45414</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>46282</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45758</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>45763</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>45783</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>45369</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>44915</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45791</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>45918</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44524</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44813</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>44490</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>45362</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44777</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45583</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>45702</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44935</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>45363</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45744</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>45096</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>45744</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>46139</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45894</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44943</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45894</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45317</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45905</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45904</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45771</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45645</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45090</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45250</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>46163</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>44974</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44897</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45580</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45008</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>46178</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>46038</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44652</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>46055</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45201</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>46079</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>46084</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45096</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45117</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>46202</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>46217</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>46218</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>46219</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>46225</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45408</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>45043</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>46231</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>46233</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>46233</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>45376</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>46241</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>46288</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45405</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>45924</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45251</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45726</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45583</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>45833</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44504</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45845</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45798</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>44596</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>44529</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44582</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>44530</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>44502</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>44537</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44825</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>44739</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44719</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44503</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44865</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44524</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>44696</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44494</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>44671</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>44713</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>44530</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44515</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>44571</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
         <v>44630</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>44530</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>44503</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>44879</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>44574</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>44686</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>44602</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>44889</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>44825</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>44582</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>44825</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44741</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>44730</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>44578</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44886</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44740</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>44874</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>44726</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>44487</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44596</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>44630</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44869</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45401</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44651</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>44957</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>45106</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>44826</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>45469</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>45118</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44900</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44783</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45086</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>44512</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45076</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45386</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>45706</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45716</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44935</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45093</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45053</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>44861</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>45110</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>45092</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>44974</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>45636</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45313</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45238</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>45356</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>44998</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>45266</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>44741</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>45742</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45043</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26228,7 +26228,7 @@
         <v>45386</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>45022</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45254</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>45583</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>45535</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44970</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>44862</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45356</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>44980</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44956</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44936</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>44966</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>45246</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45272</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>44575</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45414</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>45274</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45603</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>45400</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>44754</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45174</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45174</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44935</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>44950</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45628</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>44897</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>44644</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44896</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>44858</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>45436</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45758</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45110</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45110</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45202</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45597</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>45071</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45121</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45678</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45532</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>44889</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45678</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>45317</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45202</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45478</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45043</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45098</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>45764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45414</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>45183</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>45043</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45757</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45118</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>45715</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45215</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>44536</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>45153</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45096</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>45468</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45049</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>44599</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44999</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45330</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45201</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>44980</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45219</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>45883</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>45886</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>45966</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>45889</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45796</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45317</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>45365</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45405</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45769</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>44923</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44930</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>45520</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45891</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45888</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45043</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45888</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>45092</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>44970</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44865</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45895</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>44943</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45895</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45894</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>46139</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>45896</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>45211</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>45211</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45896</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>45867</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>45887</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45887</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45836</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45215</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>45178</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>46139</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>45898</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>45817</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45436</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45903</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45204</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45903</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45356</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45215</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45908</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45908</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>45141</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>44945</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44936</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45917</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45917</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45006</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45582</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45386</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45922</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46146</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45922</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45924</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>46146</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>45924</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>45924</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>44825</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45926</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>45930</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>45936</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45030</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>44939</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45093</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45012</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>45153</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45873</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45709</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>45943</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>44867</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>45373</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44980</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>45016</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45254</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45742</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45497</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>44861</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>44607</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45629</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45716</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45106</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45706</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45769</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45266</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>45435</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>44977</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>45960</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45709</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45960</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45961</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>45114</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>44630</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>45008</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>44783</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>44977</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45369</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>44719</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45012</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45975</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45310</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45976</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>45761</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>45153</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>45490</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>46163</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45370</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>44805</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44907</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>45117</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>45121</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45985</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39680,7 +39680,7 @@
         <v>45733</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39758,7 +39758,7 @@
         <v>45985</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39836,7 +39836,7 @@
         <v>45986</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45432</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>45986</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>44767</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45889</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45072</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>45106</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44853</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>45629</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>45629</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45478</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>45727</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45090</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>46061</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>45758</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>44936</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45205</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45446</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45446</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>45077</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45092</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>45278</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>46007</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>46006</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>45030</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45399</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>46006</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>46007</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>46006</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>46006</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>45547</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>45159</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>45121</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45699</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45699</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>44910</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>44928</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>46010</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>45637</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>46010</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45117</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>46010</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>46010</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43070,7 +43070,7 @@
         <v>45678</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>45014</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>45266</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>45049</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45049</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         <v>45266</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>46030</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>45237</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>46010</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>44974</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>46030</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>44965</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>46035</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>46037</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>46178</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>46041</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46178</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>46178</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>46038</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>46042</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>46178</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>46042</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>44834</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>46178</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>46178</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>46042</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>46178</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44596</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>46045</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>46048</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>46182</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>46046</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>46046</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45519,7 +45519,7 @@
         <v>46048</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>45771</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45546</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>45229</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>46052</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>46052</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>45030</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45030</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>46182</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>46052</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>45188</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>46182</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>45268</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45550</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>46155</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>45053</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44860</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>46188</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>44597</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45014</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>44936</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>46185</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47145,7 +47145,7 @@
         <v>46188</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>46072</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>44588</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>46076</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>46076</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47520,7 +47520,7 @@
         <v>46185</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>46079</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>44494</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>46090</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>45274</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>46072</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>46181</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45558</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>46072</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>44859</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>46093</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>46093</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48411,7 +48411,7 @@
         <v>46094</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>46094</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>46093</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>46094</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>46093</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45336</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>44582</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>45442</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>45183</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>45183</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45043</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49234,7 +49234,7 @@
         <v>45509</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49307,7 +49307,7 @@
         <v>46101</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>46196</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>45796</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49536,7 +49536,7 @@
         <v>46101</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>46196</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>45145</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49760,7 +49760,7 @@
         <v>46196</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>46106</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>46196</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>46196</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>45215</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>46108</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>46107</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>44936</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>44890</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45769</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         <v>45013</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>46198</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50661,7 +50661,7 @@
         <v>44956</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50739,7 +50739,7 @@
         <v>46198</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>46198</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50890,7 +50890,7 @@
         <v>44721</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50963,7 +50963,7 @@
         <v>46120</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>46120</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>46120</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>45217</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45191</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>46202</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>46199</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>46199</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>45733</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>46199</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>46128</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>44803</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>46199</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51927,7 +51927,7 @@
         <v>44860</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>46135</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52073,7 +52073,7 @@
         <v>46135</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>44939</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52229,7 +52229,7 @@
         <v>45891</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>46204</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45657</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>44956</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45379</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>44641</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>46203</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>44677</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>46139</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>45126</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45126</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45884</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45924</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>45268</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53271,7 +53271,7 @@
         <v>44907</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45114</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>45114</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>45833</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         <v>46206</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53641,7 +53641,7 @@
         <v>45723</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53714,7 +53714,7 @@
         <v>46206</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53787,7 +53787,7 @@
         <v>44679</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53865,7 +53865,7 @@
         <v>45359</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>44880</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54016,7 +54016,7 @@
         <v>46213</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54094,7 +54094,7 @@
         <v>46216</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45798</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>46213</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54328,7 +54328,7 @@
         <v>46213</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54406,7 +54406,7 @@
         <v>44936</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54484,7 +54484,7 @@
         <v>44936</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54562,7 +54562,7 @@
         <v>46218</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54640,7 +54640,7 @@
         <v>46217</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>46218</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>46217</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54874,7 +54874,7 @@
         <v>45769</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
         <v>44488</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>44994</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>46178</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55166,7 +55166,7 @@
         <v>45028</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55239,7 +55239,7 @@
         <v>45442</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55312,7 +55312,7 @@
         <v>45408</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>46225</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45106</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>44862</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55614,7 +55614,7 @@
         <v>44805</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>45201</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45373</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>44992</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>46231</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55989,7 +55989,7 @@
         <v>45252</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45369</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56135,7 +56135,7 @@
         <v>45673</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45128</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45741</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56359,7 +56359,7 @@
         <v>46233</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>46233</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>46279</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56593,7 +56593,7 @@
         <v>45096</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>46233</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56749,7 +56749,7 @@
         <v>46233</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>46233</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>46233</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56983,7 +56983,7 @@
         <v>45246</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45246</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>46280</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57207,7 +57207,7 @@
         <v>45174</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57280,7 +57280,7 @@
         <v>45174</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57353,7 +57353,7 @@
         <v>46280</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>45457</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57504,7 +57504,7 @@
         <v>45092</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57577,7 +57577,7 @@
         <v>45254</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         <v>45027</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>45425</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57801,7 +57801,7 @@
         <v>45581</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>46280</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57952,7 +57952,7 @@
         <v>45091</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>45369</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58103,7 +58103,7 @@
         <v>45043</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45442</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58254,7 +58254,7 @@
         <v>45008</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58327,7 +58327,7 @@
         <v>45339</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>46282</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58478,7 +58478,7 @@
         <v>46241</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>45093</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58624,7 +58624,7 @@
         <v>44992</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         <v>46244</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58770,7 +58770,7 @@
         <v>44980</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>46241</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>45453</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>46244</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59072,7 +59072,7 @@
         <v>46244</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>46244</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59223,7 +59223,7 @@
         <v>45252</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59296,7 +59296,7 @@
         <v>45636</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>45636</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59442,7 +59442,7 @@
         <v>46244</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59515,7 +59515,7 @@
         <v>44573</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59588,7 +59588,7 @@
         <v>45330</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59661,7 +59661,7 @@
         <v>44862</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59739,7 +59739,7 @@
         <v>46289</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59812,7 +59812,7 @@
         <v>46288</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59890,7 +59890,7 @@
         <v>46245</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59968,7 +59968,7 @@
         <v>46245</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>44573</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60119,7 +60119,7 @@
         <v>46050</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45110</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60275,7 +60275,7 @@
         <v>44713</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>46245</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60426,7 +60426,7 @@
         <v>46288</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>45112</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60577,7 +60577,7 @@
         <v>46052</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60650,7 +60650,7 @@
         <v>45043</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>46293</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60806,7 +60806,7 @@
         <v>44739</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45317</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60957,7 +60957,7 @@
         <v>45432</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61030,7 +61030,7 @@
         <v>45715</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61108,7 +61108,7 @@
         <v>45726</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61181,7 +61181,7 @@
         <v>45723</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61254,7 +61254,7 @@
         <v>45030</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61327,7 +61327,7 @@
         <v>45030</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61400,7 +61400,7 @@
         <v>45254</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61478,7 +61478,7 @@
         <v>45205</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61551,7 +61551,7 @@
         <v>44851</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61624,7 +61624,7 @@
         <v>45129</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61697,7 +61697,7 @@
         <v>46043</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61770,7 +61770,7 @@
         <v>45478</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61848,7 +61848,7 @@
         <v>44957</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61926,7 +61926,7 @@
         <v>45763</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -62004,7 +62004,7 @@
         <v>45403</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62077,7 +62077,7 @@
         <v>46294</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62150,7 +62150,7 @@
         <v>46072</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62228,7 +62228,7 @@
         <v>45033</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62301,7 +62301,7 @@
         <v>46258</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>45593</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>45037</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62530,7 +62530,7 @@
         <v>46258</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62608,7 +62608,7 @@
         <v>46258</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62686,7 +62686,7 @@
         <v>45030</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62759,7 +62759,7 @@
         <v>45048</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62832,7 +62832,7 @@
         <v>45777</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>46286</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>45783</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -63056,7 +63056,7 @@
         <v>45782</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -63129,7 +63129,7 @@
         <v>46258</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63207,7 +63207,7 @@
         <v>45671</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63280,7 +63280,7 @@
         <v>45784</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63353,7 +63353,7 @@
         <v>46258</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63431,7 +63431,7 @@
         <v>45784</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63509,7 +63509,7 @@
         <v>45786</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63587,7 +63587,7 @@
         <v>45786</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63665,7 +63665,7 @@
         <v>45723</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63738,7 +63738,7 @@
         <v>46260</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>46260</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63894,7 +63894,7 @@
         <v>44565</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63972,7 +63972,7 @@
         <v>45092</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -64045,7 +64045,7 @@
         <v>45453</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -64118,7 +64118,7 @@
         <v>45453</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>45310</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64264,7 +64264,7 @@
         <v>45769</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64342,7 +64342,7 @@
         <v>45790</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>46307</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64493,7 +64493,7 @@
         <v>45259</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64566,7 +64566,7 @@
         <v>45796</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64644,7 +64644,7 @@
         <v>45678</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64717,7 +64717,7 @@
         <v>45796</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64790,7 +64790,7 @@
         <v>45798</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45408</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64941,7 +64941,7 @@
         <v>45565</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -65014,7 +65014,7 @@
         <v>45798</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -65092,7 +65092,7 @@
         <v>45554</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -65165,7 +65165,7 @@
         <v>45722</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65238,7 +65238,7 @@
         <v>45803</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65311,7 +65311,7 @@
         <v>45762</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65384,7 +65384,7 @@
         <v>45804</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65462,7 +65462,7 @@
         <v>46265</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65540,7 +65540,7 @@
         <v>46265</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65618,7 +65618,7 @@
         <v>46308</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
         <v>45369</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65769,7 +65769,7 @@
         <v>46268</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65847,7 +65847,7 @@
         <v>45817</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>46311</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -66003,7 +66003,7 @@
         <v>46240</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -66076,7 +66076,7 @@
         <v>45820</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>45820</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66222,7 +66222,7 @@
         <v>45824</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66300,7 +66300,7 @@
         <v>46311</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66378,7 +66378,7 @@
         <v>45833</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66451,7 +66451,7 @@
         <v>45832</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66524,7 +66524,7 @@
         <v>45840</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66597,7 +66597,7 @@
         <v>45845</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66675,7 +66675,7 @@
         <v>45678</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66748,7 +66748,7 @@
         <v>45736</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66821,7 +66821,7 @@
         <v>45706</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66894,7 +66894,7 @@
         <v>45796</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66967,7 +66967,7 @@
         <v>45881</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -67045,7 +67045,7 @@
         <v>45883</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -67118,7 +67118,7 @@
         <v>45883</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -67191,7 +67191,7 @@
         <v>45883</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67269,7 +67269,7 @@
         <v>44130</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67342,7 +67342,7 @@
         <v>44313</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67415,7 +67415,7 @@
         <v>44230</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67488,7 +67488,7 @@
         <v>45316</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67561,7 +67561,7 @@
         <v>44638</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67639,7 +67639,7 @@
         <v>44649</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67717,7 +67717,7 @@
         <v>44551</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67790,7 +67790,7 @@
         <v>45629</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67863,7 +67863,7 @@
         <v>45571</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67936,7 +67936,7 @@
         <v>45432</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -68009,7 +68009,7 @@
         <v>44692</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -68082,7 +68082,7 @@
         <v>45571</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -68155,7 +68155,7 @@
         <v>45789</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -68228,7 +68228,7 @@
         <v>45784</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45798</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44896</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45723</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45723</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45723</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45917</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>46120</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45579</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46280</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45783</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>45922</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45139</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45411</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45086</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>45922</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>46146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>46120</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45817</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45880</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45441</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>46120</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>46283</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>45679</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45742</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>46269</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45441</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>45917</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45968</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45917</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44578</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>45964</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>46043</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>46048</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>46212</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45048</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>45336</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45782</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45789</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>45905</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>45373</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>45042</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>45884</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>46120</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45954</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>46218</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45604</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45421</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>46269</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>45833</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44622</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>45733</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>46136</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>45917</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44931</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>44746</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>45133</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>45702</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>46037</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>45013</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44977</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>46198</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>46135</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>45258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>46213</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45727</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44981</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>45016</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>46268</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>45860</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>44524</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>44557</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>44880</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45742</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45583</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>44993</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44974</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>44789</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45895</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>45086</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45334</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45936</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>45905</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>45769</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45978</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>45716</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>45985</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44957</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>45394</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>45694</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44886</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>46086</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>46198</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>46199</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>46199</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45056</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>44742</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>45201</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45797</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>46218</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>46218</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>46219</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45716</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>46233</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>46233</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45414</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>46282</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45758</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>45763</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>45783</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>45369</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>44915</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45791</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>45918</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44524</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44813</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>44490</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>45362</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44777</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45583</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>45702</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44935</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>45363</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45744</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>45096</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>45744</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>46139</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45894</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44943</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45894</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45317</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45905</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45904</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45771</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45645</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45090</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45250</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>46163</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>44974</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44897</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45580</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45008</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>46178</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>46038</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44652</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>46055</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45201</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>46079</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>46084</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45096</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45117</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>46202</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>46217</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>46218</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>46219</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>46225</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45408</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>45043</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>46231</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>46233</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>46233</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>45376</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>46241</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>46288</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45405</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>45924</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45251</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45726</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45583</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>45833</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44504</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45845</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45798</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>44596</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>44529</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44582</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>44530</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>44502</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>44537</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44825</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>44739</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44719</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44503</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44865</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44524</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>44696</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44494</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>44671</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>44713</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>44530</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44515</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>44571</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
         <v>44630</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>44530</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>44503</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>44879</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>44574</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>44686</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>44602</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>44889</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>44825</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>44582</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>44825</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44741</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>44730</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>44578</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44886</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>44740</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>44874</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>44726</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>44487</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44596</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>44630</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44869</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45401</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44651</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>44957</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>45106</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>44826</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>45469</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>45118</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44900</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44783</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45086</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>44512</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45076</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45386</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>45706</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45716</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44935</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45093</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45053</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>44861</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>45110</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>45092</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>44974</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>45636</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45313</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45238</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>45356</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>44998</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>45266</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>44741</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>45742</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45043</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26228,7 +26228,7 @@
         <v>45386</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>45022</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45254</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>45583</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>45535</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44970</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>44862</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45356</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>44980</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44956</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44936</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>44966</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>45246</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45272</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>44575</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45414</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>45274</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45603</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>45400</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>44754</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45174</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45174</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44935</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>44950</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45628</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>44897</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>44644</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44896</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>44858</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>45436</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45758</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45110</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45110</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45202</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45597</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>45071</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45121</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45678</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45532</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>44889</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45678</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>45317</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45202</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45478</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45043</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45098</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>45764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45414</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>45183</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>45043</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45757</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45118</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>45715</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>45215</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>44536</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>45153</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45096</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>45468</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45049</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>44599</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44999</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45330</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45201</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>44980</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45219</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>45883</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>45886</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>45966</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>45889</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45796</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45317</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>45365</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45405</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45769</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>44923</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44930</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>45520</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45891</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45888</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45043</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45888</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>45092</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>44970</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44865</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45895</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>44943</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45895</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45894</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>46139</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>45896</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>45211</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>45211</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45896</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>45867</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>45887</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45887</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45836</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45215</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>45178</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>46139</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>45898</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>45817</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45436</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45903</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45204</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45903</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45356</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45215</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45908</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45908</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>45141</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>44945</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44936</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45917</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45917</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45006</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45582</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45386</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45922</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46146</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45922</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45924</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>46146</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>45924</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>45924</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>44825</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45926</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>45930</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>45936</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45030</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>44939</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45093</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45012</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>45153</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45873</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45709</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>45943</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>44867</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>45373</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44980</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>45016</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45254</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45742</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45497</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>44861</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>44607</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45629</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45716</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45106</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45706</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45769</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45266</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>45435</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>44977</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>45960</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45709</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45960</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45961</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>45114</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>44630</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>45008</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>44783</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>44977</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45369</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>44719</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45012</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45975</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45310</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45976</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>45761</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>45153</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>45490</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>46163</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45370</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>44805</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44907</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>45117</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>45121</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45985</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39680,7 +39680,7 @@
         <v>45733</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39758,7 +39758,7 @@
         <v>45985</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39836,7 +39836,7 @@
         <v>45986</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45432</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>45986</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>44767</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45889</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45072</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>45106</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44853</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>45629</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>45629</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45478</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>45727</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45090</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>46061</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>45758</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>44936</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45205</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45446</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45446</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>45077</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45092</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>45278</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>46007</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>46006</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>45030</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45399</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>46006</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>46007</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>46006</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>46006</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>45547</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>45159</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>45121</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45699</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45699</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>44910</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>44928</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>46010</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>45637</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>46010</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45117</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>46010</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>46010</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43070,7 +43070,7 @@
         <v>45678</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>45014</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>45266</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>45049</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45049</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         <v>45266</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>46030</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>45237</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>46010</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>44974</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>46030</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>44965</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>46035</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>46037</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>46178</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>46041</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46178</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>46178</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>46038</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>46042</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>46178</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>46042</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>44834</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>46178</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>46178</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>46042</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>46178</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44596</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>46045</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>46048</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>46182</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>46046</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>46046</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45519,7 +45519,7 @@
         <v>46048</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>45771</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45546</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>45229</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>46052</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>46052</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>45030</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45030</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>46182</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>46052</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>45188</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>46182</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>45268</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45550</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>46155</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>45053</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44860</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>46188</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>44597</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45014</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>44936</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>46185</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47145,7 +47145,7 @@
         <v>46188</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>46072</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>44588</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>46076</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>46076</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47520,7 +47520,7 @@
         <v>46185</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>46079</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>44494</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>46090</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>45274</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>46072</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>46181</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45558</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>46072</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>44859</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>46093</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>46093</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48411,7 +48411,7 @@
         <v>46094</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>46094</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>46093</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>46094</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>46093</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45336</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>44582</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>45442</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>45183</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>45183</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45043</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49234,7 +49234,7 @@
         <v>45509</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49307,7 +49307,7 @@
         <v>46101</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>46196</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>45796</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49536,7 +49536,7 @@
         <v>46101</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>46196</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>45145</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49760,7 +49760,7 @@
         <v>46196</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>46106</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>46196</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>46196</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>45215</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>46108</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>46107</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>44936</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>44890</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45769</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         <v>45013</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>46198</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50661,7 +50661,7 @@
         <v>44956</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50739,7 +50739,7 @@
         <v>46198</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>46198</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50890,7 +50890,7 @@
         <v>44721</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50963,7 +50963,7 @@
         <v>46120</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>46120</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>46120</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>45217</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45191</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>46202</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>46199</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>46199</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>45733</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>46199</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>46128</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>44803</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>46199</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51927,7 +51927,7 @@
         <v>44860</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>46135</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52073,7 +52073,7 @@
         <v>46135</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>44939</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52229,7 +52229,7 @@
         <v>45891</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>46204</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45657</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>44956</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45379</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>44641</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>46203</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>44677</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>46139</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>45126</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45126</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45884</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45924</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>45268</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53271,7 +53271,7 @@
         <v>44907</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45114</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>45114</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>45833</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         <v>46206</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53641,7 +53641,7 @@
         <v>45723</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53714,7 +53714,7 @@
         <v>46206</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53787,7 +53787,7 @@
         <v>44679</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53865,7 +53865,7 @@
         <v>45359</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>44880</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54016,7 +54016,7 @@
         <v>46213</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54094,7 +54094,7 @@
         <v>46216</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45798</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>46213</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54328,7 +54328,7 @@
         <v>46213</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54406,7 +54406,7 @@
         <v>44936</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54484,7 +54484,7 @@
         <v>44936</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54562,7 +54562,7 @@
         <v>46218</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54640,7 +54640,7 @@
         <v>46217</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>46218</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>46217</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54874,7 +54874,7 @@
         <v>45769</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
         <v>44488</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>44994</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>46178</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55166,7 +55166,7 @@
         <v>45028</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55239,7 +55239,7 @@
         <v>45442</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55312,7 +55312,7 @@
         <v>45408</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>46225</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45106</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>44862</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55614,7 +55614,7 @@
         <v>44805</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>45201</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45373</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>44992</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>46231</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55989,7 +55989,7 @@
         <v>45252</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45369</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56135,7 +56135,7 @@
         <v>45673</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45128</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45741</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56359,7 +56359,7 @@
         <v>46233</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>46233</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>46279</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56593,7 +56593,7 @@
         <v>45096</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>46233</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56749,7 +56749,7 @@
         <v>46233</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>46233</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>46233</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56983,7 +56983,7 @@
         <v>45246</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45246</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>46280</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57207,7 +57207,7 @@
         <v>45174</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57280,7 +57280,7 @@
         <v>45174</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57353,7 +57353,7 @@
         <v>46280</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>45457</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57504,7 +57504,7 @@
         <v>45092</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57577,7 +57577,7 @@
         <v>45254</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         <v>45027</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>45425</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57801,7 +57801,7 @@
         <v>45581</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>46280</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57952,7 +57952,7 @@
         <v>45091</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>45369</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58103,7 +58103,7 @@
         <v>45043</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45442</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58254,7 +58254,7 @@
         <v>45008</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58327,7 +58327,7 @@
         <v>45339</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>46282</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58478,7 +58478,7 @@
         <v>46241</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>45093</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58624,7 +58624,7 @@
         <v>44992</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         <v>46244</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58770,7 +58770,7 @@
         <v>44980</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>46241</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>45453</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>46244</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59072,7 +59072,7 @@
         <v>46244</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>46244</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59223,7 +59223,7 @@
         <v>45252</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59296,7 +59296,7 @@
         <v>45636</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>45636</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59442,7 +59442,7 @@
         <v>46244</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59515,7 +59515,7 @@
         <v>44573</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59588,7 +59588,7 @@
         <v>45330</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59661,7 +59661,7 @@
         <v>44862</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59739,7 +59739,7 @@
         <v>46289</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59812,7 +59812,7 @@
         <v>46288</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59890,7 +59890,7 @@
         <v>46245</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59968,7 +59968,7 @@
         <v>46245</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>44573</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60119,7 +60119,7 @@
         <v>46050</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45110</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60275,7 +60275,7 @@
         <v>44713</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>46245</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60426,7 +60426,7 @@
         <v>46288</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>45112</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60577,7 +60577,7 @@
         <v>46052</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60650,7 +60650,7 @@
         <v>45043</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>46293</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60806,7 +60806,7 @@
         <v>44739</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45317</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60957,7 +60957,7 @@
         <v>45432</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61030,7 +61030,7 @@
         <v>45715</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61108,7 +61108,7 @@
         <v>45726</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61181,7 +61181,7 @@
         <v>45723</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61254,7 +61254,7 @@
         <v>45030</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61327,7 +61327,7 @@
         <v>45030</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61400,7 +61400,7 @@
         <v>45254</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61478,7 +61478,7 @@
         <v>45205</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61551,7 +61551,7 @@
         <v>44851</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61624,7 +61624,7 @@
         <v>45129</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61697,7 +61697,7 @@
         <v>46043</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61770,7 +61770,7 @@
         <v>45478</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61848,7 +61848,7 @@
         <v>44957</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61926,7 +61926,7 @@
         <v>45763</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -62004,7 +62004,7 @@
         <v>45403</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62077,7 +62077,7 @@
         <v>46294</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62150,7 +62150,7 @@
         <v>46072</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62228,7 +62228,7 @@
         <v>45033</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62301,7 +62301,7 @@
         <v>46258</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>45593</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>45037</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62530,7 +62530,7 @@
         <v>46258</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62608,7 +62608,7 @@
         <v>46258</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62686,7 +62686,7 @@
         <v>45030</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62759,7 +62759,7 @@
         <v>45048</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62832,7 +62832,7 @@
         <v>45777</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62910,7 +62910,7 @@
         <v>46286</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>45783</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -63056,7 +63056,7 @@
         <v>45782</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -63129,7 +63129,7 @@
         <v>46258</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63207,7 +63207,7 @@
         <v>45671</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63280,7 +63280,7 @@
         <v>45784</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63353,7 +63353,7 @@
         <v>46258</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63431,7 +63431,7 @@
         <v>45784</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63509,7 +63509,7 @@
         <v>45786</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63587,7 +63587,7 @@
         <v>45786</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63665,7 +63665,7 @@
         <v>45723</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63738,7 +63738,7 @@
         <v>46260</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>46260</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63894,7 +63894,7 @@
         <v>44565</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63972,7 +63972,7 @@
         <v>45092</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -64045,7 +64045,7 @@
         <v>45453</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -64118,7 +64118,7 @@
         <v>45453</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>45310</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64264,7 +64264,7 @@
         <v>45769</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64342,7 +64342,7 @@
         <v>45790</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>46307</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64493,7 +64493,7 @@
         <v>45259</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64566,7 +64566,7 @@
         <v>45796</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64644,7 +64644,7 @@
         <v>45678</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64717,7 +64717,7 @@
         <v>45796</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64790,7 +64790,7 @@
         <v>45798</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45408</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64941,7 +64941,7 @@
         <v>45565</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -65014,7 +65014,7 @@
         <v>45798</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -65092,7 +65092,7 @@
         <v>45554</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -65165,7 +65165,7 @@
         <v>45722</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65238,7 +65238,7 @@
         <v>45803</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65311,7 +65311,7 @@
         <v>45762</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65384,7 +65384,7 @@
         <v>45804</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65462,7 +65462,7 @@
         <v>46265</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65540,7 +65540,7 @@
         <v>46265</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65618,7 +65618,7 @@
         <v>46308</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
         <v>45369</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65769,7 +65769,7 @@
         <v>46268</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65847,7 +65847,7 @@
         <v>45817</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>46311</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -66003,7 +66003,7 @@
         <v>46240</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -66076,7 +66076,7 @@
         <v>45820</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>45820</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66222,7 +66222,7 @@
         <v>45824</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66300,7 +66300,7 @@
         <v>46311</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66378,7 +66378,7 @@
         <v>45833</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66451,7 +66451,7 @@
         <v>45832</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66524,7 +66524,7 @@
         <v>45840</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66597,7 +66597,7 @@
         <v>45845</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66675,7 +66675,7 @@
         <v>45678</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66748,7 +66748,7 @@
         <v>45736</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66821,7 +66821,7 @@
         <v>45706</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66894,7 +66894,7 @@
         <v>45796</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66967,7 +66967,7 @@
         <v>45881</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -67045,7 +67045,7 @@
         <v>45883</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -67118,7 +67118,7 @@
         <v>45883</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -67191,7 +67191,7 @@
         <v>45883</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67269,7 +67269,7 @@
         <v>44130</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67342,7 +67342,7 @@
         <v>44313</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67415,7 +67415,7 @@
         <v>44230</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67488,7 +67488,7 @@
         <v>45316</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67561,7 +67561,7 @@
         <v>44638</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67639,7 +67639,7 @@
         <v>44649</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67717,7 +67717,7 @@
         <v>44551</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67790,7 +67790,7 @@
         <v>45629</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67863,7 +67863,7 @@
         <v>45571</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67936,7 +67936,7 @@
         <v>45432</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -68009,7 +68009,7 @@
         <v>44692</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -68082,7 +68082,7 @@
         <v>45571</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -68155,7 +68155,7 @@
         <v>45789</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -68228,7 +68228,7 @@
         <v>45784</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45798</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44896</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45723</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45723</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45723</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45917</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>45783</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45922</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45579</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45139</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45411</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45922</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>46120</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>45880</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>46146</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45086</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45441</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>46283</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>46120</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>45679</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>46269</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>45917</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>45968</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>45441</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>45048</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>45917</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45964</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>46212</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>45782</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>46043</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>46048</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>44578</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>45336</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45789</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>45905</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45373</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45954</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>46218</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>45421</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45884</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>45833</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>46120</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>46269</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>45042</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45604</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44622</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45917</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44981</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>46198</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>46213</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>45258</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45133</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>46037</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45796</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>45860</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>46136</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>46135</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>46268</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>44931</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>45727</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>45733</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45702</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44746</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45013</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>44977</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>45016</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44524</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>44557</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45056</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45895</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44789</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>45086</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44974</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>45414</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>45936</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45721</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>45905</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>45334</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>46198</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>45978</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>46199</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>46199</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>45985</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45797</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>46218</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>46218</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>46219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45763</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45783</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>46233</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>46233</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>46282</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>44886</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>46086</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>45369</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45201</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>46316</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>45394</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44993</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44742</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45694</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44880</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45742</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45758</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45583</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45716</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>45716</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>45769</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>44957</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44915</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>45791</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>45918</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>44524</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>44813</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>45894</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>45894</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>45363</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45904</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>46163</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45771</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44652</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45744</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45744</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>46178</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>44935</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>46202</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45117</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>45250</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45405</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>46217</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>46218</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>46219</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>45726</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>46225</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>46231</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>46233</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>46233</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>46241</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>46038</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>46288</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>46055</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>45924</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>45583</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>46079</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>46084</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45833</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>44504</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>45845</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>45798</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>46139</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44943</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45251</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45317</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45008</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>45583</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45580</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45645</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45096</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45117</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45702</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45090</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45408</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45376</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45362</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>45201</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45096</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44974</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>44777</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45043</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>44897</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45174</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>44596</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>44529</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>44530</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>44582</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>44502</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>44537</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44825</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>44739</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44719</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>44503</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44865</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>44524</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>44696</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>44494</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44713</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>44671</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44530</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44515</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>44571</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44630</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>44530</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>44503</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>44879</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>44574</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>44686</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>44602</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44889</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44825</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44582</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44825</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44741</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>44730</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>44578</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>44886</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>44740</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44874</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>44726</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44596</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>44630</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44869</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45888</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45887</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45014</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45888</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45709</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>45246</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>45887</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>45405</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>45268</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>45043</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45215</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45883</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>45022</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>44825</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44865</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45894</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>45896</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>45896</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>45072</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45895</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>44862</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45895</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45043</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45090</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45202</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45532</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45883</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44783</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45898</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>45817</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45903</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45356</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45903</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45043</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45908</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45908</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45699</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45369</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>45435</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45547</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45086</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45917</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45636</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46163</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45917</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45629</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45071</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45922</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45922</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>46061</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45096</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45924</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45924</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44805</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45924</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45432</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45926</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45583</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45153</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45117</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45757</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45930</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45093</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45118</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45889</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45369</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45336</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45092</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45037</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>44980</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>44966</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45030</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45478</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45936</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>44977</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45873</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>44644</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>45012</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45943</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44862</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45076</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44860</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45706</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45386</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>45317</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>45359</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45048</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45128</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>44861</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45121</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>45425</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>46178</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>46178</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>46178</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>46178</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>46178</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>46178</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>46178</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44803</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>46182</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>46182</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>46182</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45628</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>46155</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45436</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>46185</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>46185</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>44880</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45960</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>45960</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45961</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45092</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45535</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>45373</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>46188</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>46188</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>45317</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>45219</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>45330</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>46181</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45386</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45723</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>45796</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>46196</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>46196</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>46196</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>45027</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>45373</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>45558</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44935</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>46196</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>46196</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>45478</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46198</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>46199</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>46199</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45118</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>46198</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>46198</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45975</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44980</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>46199</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>45976</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>46199</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>44977</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>45678</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>44641</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>45153</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>46202</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>44939</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45603</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44936</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>45742</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45153</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>45278</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>44858</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>46203</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>46204</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>44907</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45211</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45986</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>44936</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>45016</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45129</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45985</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45986</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>45985</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>46206</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45457</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>46206</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45497</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45706</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45310</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>45742</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>45758</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>46213</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>46213</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>45798</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>46213</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>45093</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45709</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>46217</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>46216</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>45629</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>46217</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>46218</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>46218</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>46178</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>46225</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45777</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>46006</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45782</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>46006</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>46006</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45783</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38354,7 +38354,7 @@
         <v>46006</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>45784</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>45784</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>46231</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>46233</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>46007</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>46233</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>46233</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>46007</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>46233</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>46010</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>46280</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>46010</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>46010</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>46010</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>45092</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>46280</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39650,7 +39650,7 @@
         <v>45786</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45671</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>46279</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>46233</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>46233</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>45453</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>45453</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45786</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44565</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45310</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>46010</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>45790</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>46030</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>46030</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>46035</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45678</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>46241</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>46241</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>46282</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45796</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>46038</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41228,7 +41228,7 @@
         <v>46037</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>45096</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>45796</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>46042</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>46042</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>46042</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>45259</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>46288</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>46041</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41910,7 +41910,7 @@
         <v>46244</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>46288</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45798</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>45798</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>46244</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>46244</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>46244</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>46245</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>45565</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>46046</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42665,7 +42665,7 @@
         <v>46048</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42738,7 +42738,7 @@
         <v>46245</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45408</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>46048</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>46046</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>46045</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>45554</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>46244</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>46245</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>46050</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>45722</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>46052</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45803</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43639,7 +43639,7 @@
         <v>45804</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>46289</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>46052</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>46052</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43936,7 +43936,7 @@
         <v>45762</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>45369</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>46052</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>46293</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44238,7 +44238,7 @@
         <v>45817</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45820</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>46072</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45820</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44540,7 +44540,7 @@
         <v>46076</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44613,7 +44613,7 @@
         <v>45824</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>45266</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>46076</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>46294</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>46079</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45832</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>46043</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>46072</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45490</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45833</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>45763</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>44930</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>46072</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>46072</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>46090</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45840</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46093</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>46093</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>46093</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>46093</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>46094</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>46094</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46249,7 +46249,7 @@
         <v>46094</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46327,7 +46327,7 @@
         <v>44936</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46400,7 +46400,7 @@
         <v>46286</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45678</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>46101</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>46101</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46702,7 +46702,7 @@
         <v>45845</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>46258</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>46258</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45736</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -47009,7 +47009,7 @@
         <v>46107</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>46106</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>46108</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47238,7 +47238,7 @@
         <v>46258</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>46258</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>46258</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>44890</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>45706</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>46120</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47696,7 +47696,7 @@
         <v>46120</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>46120</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45414</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>46260</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>46260</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48081,7 +48081,7 @@
         <v>45723</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48154,7 +48154,7 @@
         <v>45769</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>45796</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>46265</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>46128</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>45881</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>45883</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45883</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>44582</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>46265</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48836,7 +48836,7 @@
         <v>45836</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48909,7 +48909,7 @@
         <v>45884</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45889</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45202</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45924</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>46308</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>46307</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>46135</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49430,7 +49430,7 @@
         <v>46135</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>45657</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49586,7 +49586,7 @@
         <v>45365</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49664,7 +49664,7 @@
         <v>45833</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45966</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45442</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45891</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45891</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45520</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>44936</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>45030</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>46240</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>46139</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45886</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>44889</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>46268</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>46311</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45178</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50779,7 +50779,7 @@
         <v>45028</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>44910</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>46311</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -51008,7 +51008,7 @@
         <v>46280</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51086,7 +51086,7 @@
         <v>45106</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45796</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51232,7 +51232,7 @@
         <v>46316</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
         <v>46315</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>45201</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51451,7 +51451,7 @@
         <v>46139</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>46315</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51602,7 +51602,7 @@
         <v>46139</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>45867</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>46316</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>45369</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>45215</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>45678</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44936</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>44974</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>44943</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>45174</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45174</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>46146</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>46146</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         <v>45453</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45238</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52717,7 +52717,7 @@
         <v>45049</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52790,7 +52790,7 @@
         <v>45091</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52868,7 +52868,7 @@
         <v>45112</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52941,7 +52941,7 @@
         <v>44677</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>44834</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53092,7 +53092,7 @@
         <v>44741</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53165,7 +53165,7 @@
         <v>44965</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45014</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>44956</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>45356</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45636</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>44719</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53608,7 +53608,7 @@
         <v>45581</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53681,7 +53681,7 @@
         <v>44573</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>45414</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>44998</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>44512</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53978,7 +53978,7 @@
         <v>44970</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>44980</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54129,7 +54129,7 @@
         <v>45386</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54207,7 +54207,7 @@
         <v>44721</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45114</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>45629</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45098</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         <v>44805</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>45117</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>45582</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54733,7 +54733,7 @@
         <v>45597</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54806,7 +54806,7 @@
         <v>45469</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>45726</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54952,7 +54952,7 @@
         <v>44713</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45121</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55103,7 +55103,7 @@
         <v>45201</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55176,7 +55176,7 @@
         <v>45030</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45030</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         <v>44853</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55395,7 +55395,7 @@
         <v>44999</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>45110</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>44826</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45442</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>45442</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>45008</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>44980</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55931,7 +55931,7 @@
         <v>45013</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -56004,7 +56004,7 @@
         <v>45229</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56077,7 +56077,7 @@
         <v>45764</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56150,7 +56150,7 @@
         <v>45715</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56228,7 +56228,7 @@
         <v>44992</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56301,7 +56301,7 @@
         <v>44575</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56374,7 +56374,7 @@
         <v>44957</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56452,7 +56452,7 @@
         <v>44945</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56525,7 +56525,7 @@
         <v>45093</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56598,7 +56598,7 @@
         <v>45110</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56676,7 +56676,7 @@
         <v>45274</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56749,7 +56749,7 @@
         <v>45254</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45077</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45509</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>45043</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45183</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57119,7 +57119,7 @@
         <v>45049</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>45049</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>44939</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>45012</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57411,7 +57411,7 @@
         <v>45237</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>45769</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57567,7 +57567,7 @@
         <v>45769</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         <v>45769</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57713,7 +57713,7 @@
         <v>45733</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57791,7 +57791,7 @@
         <v>44860</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57864,7 +57864,7 @@
         <v>45741</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57942,7 +57942,7 @@
         <v>44896</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>44900</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58098,7 +58098,7 @@
         <v>45769</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>44897</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58249,7 +58249,7 @@
         <v>44928</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58327,7 +58327,7 @@
         <v>44923</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>44907</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58478,7 +58478,7 @@
         <v>44588</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>45436</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58629,7 +58629,7 @@
         <v>44783</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45716</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>45106</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45379</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>45339</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>45408</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59067,7 +59067,7 @@
         <v>45254</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>44607</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>44950</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>45092</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59364,7 +59364,7 @@
         <v>45006</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59442,7 +59442,7 @@
         <v>45030</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59515,7 +59515,7 @@
         <v>45030</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59588,7 +59588,7 @@
         <v>44994</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59661,7 +59661,7 @@
         <v>45110</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59734,7 +59734,7 @@
         <v>45110</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59807,7 +59807,7 @@
         <v>45478</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59885,7 +59885,7 @@
         <v>45370</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59963,7 +59963,7 @@
         <v>44957</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60041,7 +60041,7 @@
         <v>44494</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60114,7 +60114,7 @@
         <v>44974</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>45771</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60270,7 +60270,7 @@
         <v>45637</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60343,7 +60343,7 @@
         <v>45593</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60421,7 +60421,7 @@
         <v>45126</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60494,7 +60494,7 @@
         <v>45126</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60567,7 +60567,7 @@
         <v>45141</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60645,7 +60645,7 @@
         <v>45145</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>45400</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60796,7 +60796,7 @@
         <v>45403</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>44935</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60947,7 +60947,7 @@
         <v>45114</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45114</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61098,7 +61098,7 @@
         <v>45546</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61171,7 +61171,7 @@
         <v>45356</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61244,7 +61244,7 @@
         <v>45092</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61317,7 +61317,7 @@
         <v>45266</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61390,7 +61390,7 @@
         <v>45033</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61463,7 +61463,7 @@
         <v>44536</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61536,7 +61536,7 @@
         <v>44596</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61614,7 +61614,7 @@
         <v>44573</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>45550</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61760,7 +61760,7 @@
         <v>45727</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61838,7 +61838,7 @@
         <v>45159</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61911,7 +61911,7 @@
         <v>45432</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61984,7 +61984,7 @@
         <v>45043</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62062,7 +62062,7 @@
         <v>45183</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62135,7 +62135,7 @@
         <v>45183</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62208,7 +62208,7 @@
         <v>45673</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62281,7 +62281,7 @@
         <v>45053</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>45217</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62427,7 +62427,7 @@
         <v>45636</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62500,7 +62500,7 @@
         <v>45313</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>45121</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>45205</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45205</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62802,7 +62802,7 @@
         <v>44679</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62880,7 +62880,7 @@
         <v>45761</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62958,7 +62958,7 @@
         <v>44630</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -63031,7 +63031,7 @@
         <v>45211</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -63104,7 +63104,7 @@
         <v>44651</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63177,7 +63177,7 @@
         <v>45446</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63250,7 +63250,7 @@
         <v>45446</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63323,7 +63323,7 @@
         <v>45254</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63396,7 +63396,7 @@
         <v>45215</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63469,7 +63469,7 @@
         <v>45188</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63542,7 +63542,7 @@
         <v>45715</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         <v>45723</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63693,7 +63693,7 @@
         <v>45699</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63766,7 +63766,7 @@
         <v>45204</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63844,7 +63844,7 @@
         <v>45468</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63917,7 +63917,7 @@
         <v>45401</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63995,7 +63995,7 @@
         <v>45274</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -64068,7 +64068,7 @@
         <v>45252</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -64141,7 +64141,7 @@
         <v>45191</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64214,7 +64214,7 @@
         <v>45758</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64292,7 +64292,7 @@
         <v>45254</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64370,7 +64370,7 @@
         <v>45246</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64443,7 +64443,7 @@
         <v>45246</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64516,7 +64516,7 @@
         <v>44956</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64594,7 +64594,7 @@
         <v>44956</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64672,7 +64672,7 @@
         <v>45252</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64745,7 +64745,7 @@
         <v>45272</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64823,7 +64823,7 @@
         <v>45399</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64901,7 +64901,7 @@
         <v>45317</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64979,7 +64979,7 @@
         <v>44862</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -65052,7 +65052,7 @@
         <v>45716</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -65130,7 +65130,7 @@
         <v>45266</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65203,7 +65203,7 @@
         <v>44859</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65281,7 +65281,7 @@
         <v>45330</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65354,7 +65354,7 @@
         <v>45266</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65427,7 +65427,7 @@
         <v>44851</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65500,7 +65500,7 @@
         <v>45106</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65573,7 +65573,7 @@
         <v>45043</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65651,7 +65651,7 @@
         <v>44767</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65724,7 +65724,7 @@
         <v>45268</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65797,7 +65797,7 @@
         <v>44599</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65870,7 +65870,7 @@
         <v>44597</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65943,7 +65943,7 @@
         <v>45678</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -66016,7 +66016,7 @@
         <v>44754</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -66089,7 +66089,7 @@
         <v>44739</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66162,7 +66162,7 @@
         <v>44970</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66240,7 +66240,7 @@
         <v>45215</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66313,7 +66313,7 @@
         <v>45106</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66386,7 +66386,7 @@
         <v>45053</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66459,7 +66459,7 @@
         <v>45733</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66537,7 +66537,7 @@
         <v>44867</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66615,7 +66615,7 @@
         <v>45043</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66688,7 +66688,7 @@
         <v>44861</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66766,7 +66766,7 @@
         <v>45008</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66839,7 +66839,7 @@
         <v>44936</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66917,7 +66917,7 @@
         <v>44936</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66995,7 +66995,7 @@
         <v>45030</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -67068,7 +67068,7 @@
         <v>45174</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -67141,7 +67141,7 @@
         <v>45174</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67214,7 +67214,7 @@
         <v>44992</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67287,7 +67287,7 @@
         <v>44313</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67360,7 +67360,7 @@
         <v>44130</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67433,7 +67433,7 @@
         <v>44230</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67506,7 +67506,7 @@
         <v>44638</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67584,7 +67584,7 @@
         <v>44649</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67662,7 +67662,7 @@
         <v>44551</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67735,7 +67735,7 @@
         <v>44692</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67808,7 +67808,7 @@
         <v>45316</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67881,7 +67881,7 @@
         <v>45629</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67954,7 +67954,7 @@
         <v>45571</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -68027,7 +68027,7 @@
         <v>45432</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -68100,7 +68100,7 @@
         <v>45571</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -68173,7 +68173,7 @@
         <v>45789</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68246,7 +68246,7 @@
         <v>45784</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>

--- a/Översikt NORRKÖPING.xlsx
+++ b/Översikt NORRKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45798</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44896</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45723</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45723</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45723</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45917</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>45783</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45922</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>46120</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45579</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45139</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45411</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45922</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>46120</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>45880</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>46146</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45086</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45441</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>46283</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>46120</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>45679</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45723</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>46269</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>45917</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>45968</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>45441</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>45048</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>45917</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45964</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>46212</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>45782</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>46043</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>46048</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>44578</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>45336</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45789</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>45905</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45373</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45954</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>46218</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>45421</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45884</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>45833</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>46120</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>46269</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>45042</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45604</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44622</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45917</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44981</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>46198</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>46213</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>45258</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45133</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>46037</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45796</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>45860</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>46136</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>46135</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>46268</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>44931</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>45727</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>45733</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45702</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44746</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45013</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>44977</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>45016</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44524</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>44557</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45056</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45895</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44789</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>45086</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44974</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>45414</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>45936</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45721</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>45905</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>45334</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>46198</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>45978</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>46199</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>46199</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>45985</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45797</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>46218</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>46218</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>46219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45763</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45783</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>46233</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>46233</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>46282</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>44886</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>46086</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>45369</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45201</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>46316</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>45394</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44993</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44742</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45694</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44880</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45742</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45758</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45583</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45716</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>45716</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>45769</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>44957</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44915</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>45791</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>45918</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>44524</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>44813</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>45894</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>45894</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>45363</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45904</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>46163</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45771</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44652</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45744</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45744</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>46178</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>44935</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>46202</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45117</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>45250</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45405</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>46217</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>46218</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>46219</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>45726</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>46225</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>46231</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>46233</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>46233</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>46241</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>46038</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>46288</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>46055</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>45924</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>45583</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>46079</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>46084</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45833</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>44504</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>45845</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>45798</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>46139</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>44943</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45251</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45317</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45008</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>45583</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45580</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45645</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45096</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45117</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45702</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45090</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45408</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45376</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45362</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>45201</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45096</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44974</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>44777</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45043</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>44897</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45174</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>44596</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>44529</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>44530</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>44582</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>44502</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>44537</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44825</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>44739</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>44719</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>44503</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44865</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>44524</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>44696</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>44494</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44713</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>44671</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44530</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44515</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>44571</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44630</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>44530</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>44503</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>44879</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>44574</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>44686</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>44602</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44889</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44825</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44582</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44825</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44741</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>44730</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>44578</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>44886</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>44740</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44874</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>44726</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44596</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>44630</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44869</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45888</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45887</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45014</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45888</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45709</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>45246</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>45887</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>45405</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>45268</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>45043</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45215</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45883</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>45022</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>44825</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44865</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45894</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>45896</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>45896</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>45072</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45895</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>44862</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45895</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45043</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45090</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45202</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45532</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45883</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44783</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45898</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>45817</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45903</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45356</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45903</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45043</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45908</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45908</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45699</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45369</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>45435</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45547</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45086</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45917</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45636</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46163</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45917</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45629</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45071</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45922</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45922</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>46061</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45096</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45924</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45924</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44805</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45924</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45432</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45926</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45583</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45153</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45117</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45757</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45930</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45093</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45118</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45889</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45369</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45336</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45092</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45037</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>44980</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>44966</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45030</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45478</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45936</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>44977</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45873</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>44644</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>45012</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45943</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44862</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45076</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44860</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45706</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45386</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>45317</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>45359</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45048</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45128</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>44861</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45121</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>45425</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>46178</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>46178</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>46178</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>46178</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>46178</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>46178</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>46178</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44803</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>46182</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>46182</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>46182</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45628</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>46155</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45436</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>46185</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>46185</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>44880</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45960</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>45960</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45961</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45092</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45535</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>45373</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>46188</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>46188</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>45317</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>45219</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>45330</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>46181</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45386</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45723</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>45796</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>46196</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>46196</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>46196</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>45027</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>45373</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>45558</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44935</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>46196</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>46196</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>45478</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46198</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>46199</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>46199</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45118</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>46198</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>46198</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45975</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>44980</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>46199</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>45976</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>46199</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>44977</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>45678</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>44641</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>45153</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>46202</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>44939</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45603</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>44936</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>45742</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45153</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>45278</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>44858</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>46203</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>46204</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>44907</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45211</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45986</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>44936</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>45016</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45129</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45985</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45986</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>45985</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>46206</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45457</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>46206</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45497</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45706</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45310</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>45742</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>45758</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>46213</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>46213</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>45798</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>46213</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>45093</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45709</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>46217</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>46216</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>45629</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>46217</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>46218</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>46218</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>46178</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>46225</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45777</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>46006</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45782</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>46006</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>46006</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45783</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38354,7 +38354,7 @@
         <v>46006</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>45784</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>45784</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>46231</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>46233</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>46007</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>46233</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>46233</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>46007</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>46233</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>46010</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>46280</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>46010</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>46010</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>46010</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>45092</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>46280</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39650,7 +39650,7 @@
         <v>45786</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45671</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>46279</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>46233</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>46233</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>45453</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>45453</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45786</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44565</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45310</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>46010</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>45790</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>46030</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>46030</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>46035</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45678</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>46241</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>46241</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>46282</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45796</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>46038</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41228,7 +41228,7 @@
         <v>46037</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>45096</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>45796</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>46042</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>46042</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>46042</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>45259</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>46288</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>46041</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41910,7 +41910,7 @@
         <v>46244</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>46288</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45798</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>45798</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>46244</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>46244</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>46244</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>46245</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>45565</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>46046</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42665,7 +42665,7 @@
         <v>46048</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42738,7 +42738,7 @@
         <v>46245</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45408</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>46048</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>46046</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>46045</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>45554</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>46244</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>46245</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>46050</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>45722</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>46052</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45803</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43639,7 +43639,7 @@
         <v>45804</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>46289</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>46052</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>46052</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43936,7 +43936,7 @@
         <v>45762</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>45369</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>46052</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>46293</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44238,7 +44238,7 @@
         <v>45817</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45820</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>46072</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45820</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44540,7 +44540,7 @@
         <v>46076</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44613,7 +44613,7 @@
         <v>45824</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>45266</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         <v>46076</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>46294</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>46079</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45832</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>46043</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>46072</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45490</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45833</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>45763</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>44930</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>46072</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>46072</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>46090</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45840</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46093</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>46093</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>46093</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>46093</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>46094</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>46094</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46249,7 +46249,7 @@
         <v>46094</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46327,7 +46327,7 @@
         <v>44936</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46400,7 +46400,7 @@
         <v>46286</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45678</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>46101</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>46101</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46702,7 +46702,7 @@
         <v>45845</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>46258</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>46258</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45736</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -47009,7 +47009,7 @@
         <v>46107</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>46106</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>46108</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47238,7 +47238,7 @@
         <v>46258</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>46258</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>46258</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>44890</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>45706</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>46120</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47696,7 +47696,7 @@
         <v>46120</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>46120</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45414</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>46260</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>46260</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48081,7 +48081,7 @@
         <v>45723</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48154,7 +48154,7 @@
         <v>45769</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>45796</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>46265</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>46128</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>45881</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>45883</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45883</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>44582</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>46265</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48836,7 +48836,7 @@
         <v>45836</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48909,7 +48909,7 @@
         <v>45884</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45889</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45202</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45924</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>46308</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>46307</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>46135</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49430,7 +49430,7 @@
         <v>46135</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>45657</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49586,7 +49586,7 @@
         <v>45365</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49664,7 +49664,7 @@
         <v>45833</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45966</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>45442</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45891</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45891</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45520</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>44936</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>45030</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>46240</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>46139</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45886</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>44889</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>46268</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>46311</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45178</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50779,7 +50779,7 @@
         <v>45028</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>44910</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>46311</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -51008,7 +51008,7 @@
         <v>46280</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51086,7 +51086,7 @@
         <v>45106</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45796</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51232,7 +51232,7 @@
         <v>46316</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
         <v>46315</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>45201</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51451,7 +51451,7 @@
         <v>46139</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>46315</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51602,7 +51602,7 @@
         <v>46139</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>45867</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>46316</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>45369</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>45215</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>45678</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44936</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>44974</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>44943</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>45174</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45174</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>46146</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>46146</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         <v>45453</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45238</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52717,7 +52717,7 @@
         <v>45049</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52790,7 +52790,7 @@
         <v>45091</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52868,7 +52868,7 @@
         <v>45112</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52941,7 +52941,7 @@
         <v>44677</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>44834</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53092,7 +53092,7 @@
         <v>44741</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53165,7 +53165,7 @@
         <v>44965</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45014</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>44956</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>45356</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45636</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>44719</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53608,7 +53608,7 @@
         <v>45581</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53681,7 +53681,7 @@
         <v>44573</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>45414</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>44998</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>44512</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53978,7 +53978,7 @@
         <v>44970</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>44980</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54129,7 +54129,7 @@
         <v>45386</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54207,7 +54207,7 @@
         <v>44721</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>45114</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>45629</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45098</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         <v>44805</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>45117</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>45582</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54733,7 +54733,7 @@
         <v>45597</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54806,7 +54806,7 @@
         <v>45469</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>45726</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54952,7 +54952,7 @@
         <v>44713</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55025,7 +55025,7 @@
         <v>45121</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55103,7 +55103,7 @@
         <v>45201</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55176,7 +55176,7 @@
         <v>45030</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45030</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         <v>44853</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55395,7 +55395,7 @@
         <v>44999</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>45110</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>44826</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45442</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>45442</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>45008</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>44980</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55931,7 +55931,7 @@
         <v>45013</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -56004,7 +56004,7 @@
         <v>45229</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56077,7 +56077,7 @@
         <v>45764</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56150,7 +56150,7 @@
         <v>45715</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56228,7 +56228,7 @@
         <v>44992</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56301,7 +56301,7 @@
         <v>44575</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56374,7 +56374,7 @@
         <v>44957</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56452,7 +56452,7 @@
         <v>44945</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56525,7 +56525,7 @@
         <v>45093</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56598,7 +56598,7 @@
         <v>45110</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56676,7 +56676,7 @@
         <v>45274</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56749,7 +56749,7 @@
         <v>45254</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45077</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45509</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>45043</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45183</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57119,7 +57119,7 @@
         <v>45049</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>45049</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>44939</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>45012</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57411,7 +57411,7 @@
         <v>45237</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>45769</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57567,7 +57567,7 @@
         <v>45769</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         <v>45769</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57713,7 +57713,7 @@
         <v>45733</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57791,7 +57791,7 @@
         <v>44860</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57864,7 +57864,7 @@
         <v>45741</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57942,7 +57942,7 @@
         <v>44896</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>44900</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58098,7 +58098,7 @@
         <v>45769</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>44897</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58249,7 +58249,7 @@
         <v>44928</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58327,7 +58327,7 @@
         <v>44923</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>44907</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58478,7 +58478,7 @@
         <v>44588</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>45436</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58629,7 +58629,7 @@
         <v>44783</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45716</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>45106</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45379</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>45339</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>45408</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59067,7 +59067,7 @@
         <v>45254</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>44607</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>44950</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>45092</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59364,7 +59364,7 @@
         <v>45006</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59442,7 +59442,7 @@
         <v>45030</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59515,7 +59515,7 @@
         <v>45030</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59588,7 +59588,7 @@
         <v>44994</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59661,7 +59661,7 @@
         <v>45110</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59734,7 +59734,7 @@
         <v>45110</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59807,7 +59807,7 @@
         <v>45478</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59885,7 +59885,7 @@
         <v>45370</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59963,7 +59963,7 @@
         <v>44957</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60041,7 +60041,7 @@
         <v>44494</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60114,7 +60114,7 @@
         <v>44974</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>45771</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60270,7 +60270,7 @@
         <v>45637</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60343,7 +60343,7 @@
         <v>45593</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60421,7 +60421,7 @@
         <v>45126</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60494,7 +60494,7 @@
         <v>45126</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60567,7 +60567,7 @@
         <v>45141</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60645,7 +60645,7 @@
         <v>45145</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>45400</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60796,7 +60796,7 @@
         <v>45403</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60869,7 +60869,7 @@
         <v>44935</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60947,7 +60947,7 @@
         <v>45114</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45114</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61098,7 +61098,7 @@
         <v>45546</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61171,7 +61171,7 @@
         <v>45356</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61244,7 +61244,7 @@
         <v>45092</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61317,7 +61317,7 @@
         <v>45266</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61390,7 +61390,7 @@
         <v>45033</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61463,7 +61463,7 @@
         <v>44536</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61536,7 +61536,7 @@
         <v>44596</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61614,7 +61614,7 @@
         <v>44573</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>45550</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61760,7 +61760,7 @@
         <v>45727</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61838,7 +61838,7 @@
         <v>45159</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61911,7 +61911,7 @@
         <v>45432</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61984,7 +61984,7 @@
         <v>45043</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62062,7 +62062,7 @@
         <v>45183</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62135,7 +62135,7 @@
         <v>45183</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62208,7 +62208,7 @@
         <v>45673</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62281,7 +62281,7 @@
         <v>45053</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>45217</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62427,7 +62427,7 @@
         <v>45636</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62500,7 +62500,7 @@
         <v>45313</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>45121</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>45205</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>45205</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62802,7 +62802,7 @@
         <v>44679</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62880,7 +62880,7 @@
         <v>45761</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62958,7 +62958,7 @@
         <v>44630</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -63031,7 +63031,7 @@
         <v>45211</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -63104,7 +63104,7 @@
         <v>44651</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63177,7 +63177,7 @@
         <v>45446</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63250,7 +63250,7 @@
         <v>45446</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63323,7 +63323,7 @@
         <v>45254</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63396,7 +63396,7 @@
         <v>45215</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63469,7 +63469,7 @@
         <v>45188</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63542,7 +63542,7 @@
         <v>45715</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         <v>45723</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63693,7 +63693,7 @@
         <v>45699</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63766,7 +63766,7 @@
         <v>45204</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63844,7 +63844,7 @@
         <v>45468</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63917,7 +63917,7 @@
         <v>45401</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63995,7 +63995,7 @@
         <v>45274</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -64068,7 +64068,7 @@
         <v>45252</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -64141,7 +64141,7 @@
         <v>45191</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64214,7 +64214,7 @@
         <v>45758</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64292,7 +64292,7 @@
         <v>45254</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64370,7 +64370,7 @@
         <v>45246</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64443,7 +64443,7 @@
         <v>45246</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64516,7 +64516,7 @@
         <v>44956</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64594,7 +64594,7 @@
         <v>44956</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64672,7 +64672,7 @@
         <v>45252</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64745,7 +64745,7 @@
         <v>45272</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64823,7 +64823,7 @@
         <v>45399</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64901,7 +64901,7 @@
         <v>45317</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64979,7 +64979,7 @@
         <v>44862</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -65052,7 +65052,7 @@
         <v>45716</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -65130,7 +65130,7 @@
         <v>45266</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65203,7 +65203,7 @@
         <v>44859</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65281,7 +65281,7 @@
         <v>45330</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65354,7 +65354,7 @@
         <v>45266</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65427,7 +65427,7 @@
         <v>44851</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65500,7 +65500,7 @@
         <v>45106</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65573,7 +65573,7 @@
         <v>45043</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65651,7 +65651,7 @@
         <v>44767</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65724,7 +65724,7 @@
         <v>45268</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65797,7 +65797,7 @@
         <v>44599</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65870,7 +65870,7 @@
         <v>44597</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65943,7 +65943,7 @@
         <v>45678</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -66016,7 +66016,7 @@
         <v>44754</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -66089,7 +66089,7 @@
         <v>44739</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66162,7 +66162,7 @@
         <v>44970</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66240,7 +66240,7 @@
         <v>45215</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66313,7 +66313,7 @@
         <v>45106</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66386,7 +66386,7 @@
         <v>45053</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66459,7 +66459,7 @@
         <v>45733</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66537,7 +66537,7 @@
         <v>44867</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66615,7 +66615,7 @@
         <v>45043</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66688,7 +66688,7 @@
         <v>44861</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66766,7 +66766,7 @@
         <v>45008</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66839,7 +66839,7 @@
         <v>44936</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66917,7 +66917,7 @@
         <v>44936</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66995,7 +66995,7 @@
         <v>45030</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -67068,7 +67068,7 @@
         <v>45174</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -67141,7 +67141,7 @@
         <v>45174</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67214,7 +67214,7 @@
         <v>44992</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67287,7 +67287,7 @@
         <v>44313</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67360,7 +67360,7 @@
         <v>44130</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67433,7 +67433,7 @@
         <v>44230</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67506,7 +67506,7 @@
         <v>44638</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67584,7 +67584,7 @@
         <v>44649</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67662,7 +67662,7 @@
         <v>44551</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67735,7 +67735,7 @@
         <v>44692</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67808,7 +67808,7 @@
         <v>45316</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67881,7 +67881,7 @@
         <v>45629</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67954,7 +67954,7 @@
         <v>45571</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -68027,7 +68027,7 @@
         <v>45432</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -68100,7 +68100,7 @@
         <v>45571</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -68173,7 +68173,7 @@
         <v>45789</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68246,7 +68246,7 @@
         <v>45784</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
